--- a/padron de ofertas.xlsx
+++ b/padron de ofertas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sucursal17\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13FFD1F-9BF2-4243-9D91-4F40F00F1074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F28192-DB94-4CAD-8DD4-BFDAE08DD422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{50A341D9-31B7-464A-BF33-600D29708FF5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{50A341D9-31B7-464A-BF33-600D29708FF5}"/>
   </bookViews>
   <sheets>
     <sheet name="OFERTAS" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5842" uniqueCount="1832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6046" uniqueCount="1944">
   <si>
     <t>COD_INT</t>
   </si>
@@ -5539,19 +5539,356 @@
   </si>
   <si>
     <t xml:space="preserve">EDUS HILERET FORTE C/STEVIA SOB 50X               </t>
+  </si>
+  <si>
+    <t>7628|14149</t>
+  </si>
+  <si>
+    <t>1 ROTI S SANDWICH JyQ TRIANGULO + 1 GAS  PEPSI ORIGINAL LATA 354X</t>
+  </si>
+  <si>
+    <t>$           5.197,00</t>
+  </si>
+  <si>
+    <t> $    4.248,50</t>
+  </si>
+  <si>
+    <t> $                  948,50</t>
+  </si>
+  <si>
+    <t>8996|14149</t>
+  </si>
+  <si>
+    <t>1 ROTI SANDWICH MILA DE POLLO x1 + 1 GAS  PEPSI ORIGINAL LATA 354X</t>
+  </si>
+  <si>
+    <t>$           7.897,00</t>
+  </si>
+  <si>
+    <t> $    6.948,50</t>
+  </si>
+  <si>
+    <t> $                  948,50</t>
+  </si>
+  <si>
+    <t>7426|14149</t>
+  </si>
+  <si>
+    <t>1 ROTI SANDWICH MILA CARNE x 1 + 1 GAS  PEPSI ORIGINAL LATA 354X</t>
+  </si>
+  <si>
+    <t>$           7.997,00</t>
+  </si>
+  <si>
+    <t> $    7.048,50</t>
+  </si>
+  <si>
+    <t>6893|14149</t>
+  </si>
+  <si>
+    <t>1 ROTI S SANDWICH JAMON Y QUESO  X6 + 1 GAS  PEPSI ORIGINAL LATA 354X</t>
+  </si>
+  <si>
+    <t>$           9.197,00</t>
+  </si>
+  <si>
+    <t> $    8.248,50</t>
+  </si>
+  <si>
+    <t>Sin Indicar        </t>
+  </si>
+  <si>
+    <t>ACGI LEGITIMO GIR 900X                           </t>
+  </si>
+  <si>
+    <t> $           4.498,75</t>
+  </si>
+  <si>
+    <t> $           3.599,00</t>
+  </si>
+  <si>
+    <t> $                899,75</t>
+  </si>
+  <si>
+    <t>CONP CUMANA ATUN E/A DESM 170X                   </t>
+  </si>
+  <si>
+    <t> $           1.937,50</t>
+  </si>
+  <si>
+    <t> $           1.550,00</t>
+  </si>
+  <si>
+    <t> $                387,50</t>
+  </si>
+  <si>
+    <t>CONP CUMANA ATUN NAT DESM 170X                   </t>
+  </si>
+  <si>
+    <t>HARM PRESTO PRONTA 500X                          </t>
+  </si>
+  <si>
+    <t> $           1.812,50</t>
+  </si>
+  <si>
+    <t> $           1.450,00</t>
+  </si>
+  <si>
+    <t> $                362,50</t>
+  </si>
+  <si>
+    <t>HARL FLORENCIA LEUD 1X                           </t>
+  </si>
+  <si>
+    <t> $           1.748,75</t>
+  </si>
+  <si>
+    <t> $           1.399,00</t>
+  </si>
+  <si>
+    <t> $                349,75</t>
+  </si>
+  <si>
+    <t>ARR D.HERMANO L/F 1X                             </t>
+  </si>
+  <si>
+    <t> $           1.623,75</t>
+  </si>
+  <si>
+    <t> $           1.299,00</t>
+  </si>
+  <si>
+    <t> $                324,75</t>
+  </si>
+  <si>
+    <t>ARR  MARIA LARGO FINO 1X                         </t>
+  </si>
+  <si>
+    <t> $           1.498,75</t>
+  </si>
+  <si>
+    <t> $           1.199,00</t>
+  </si>
+  <si>
+    <t> $                299,75</t>
+  </si>
+  <si>
+    <t>HART FLORENCIA 3/0 1X                             </t>
+  </si>
+  <si>
+    <t> $           1.187,50</t>
+  </si>
+  <si>
+    <t> $                950,00</t>
+  </si>
+  <si>
+    <t> $                237,50</t>
+  </si>
+  <si>
+    <t>FIDO FAVORITA MOST 500X                          </t>
+  </si>
+  <si>
+    <t> $           1.050,00</t>
+  </si>
+  <si>
+    <t> $                840,00</t>
+  </si>
+  <si>
+    <t> $                210,00</t>
+  </si>
+  <si>
+    <t>FIDO FAVORITA CODITO RAY 500X                    </t>
+  </si>
+  <si>
+    <t>FIDO FAVORITA TIRAB 500X                         </t>
+  </si>
+  <si>
+    <t>FIDO FAVORITA TALL 500X                          </t>
+  </si>
+  <si>
+    <t>FIDO FAVORITA SPAG 500X                          </t>
+  </si>
+  <si>
+    <t>PURE SAB.VALLE T/B 520X                          </t>
+  </si>
+  <si>
+    <t> $                937,50</t>
+  </si>
+  <si>
+    <t> $                750,00</t>
+  </si>
+  <si>
+    <t> $                187,50</t>
+  </si>
+  <si>
+    <t>ARV  SAB.VALLE SEC REM T/P  340X                 </t>
+  </si>
+  <si>
+    <t> $                825,00</t>
+  </si>
+  <si>
+    <t> $                660,00</t>
+  </si>
+  <si>
+    <t> $                165,00</t>
+  </si>
+  <si>
+    <t>AZUC LA PROVIDENCIA 1X                           </t>
+  </si>
+  <si>
+    <t>CAFI DOLCA SUAVE + AROMA FCO 100X                </t>
+  </si>
+  <si>
+    <t> $           9.062,50</t>
+  </si>
+  <si>
+    <t> $           7.250,00</t>
+  </si>
+  <si>
+    <t>CAFI DOLCA CLAS + AROMA 100X                     </t>
+  </si>
+  <si>
+    <t>CERV BUDWEISER LAT 473X                          </t>
+  </si>
+  <si>
+    <t> $           2.231,25</t>
+  </si>
+  <si>
+    <t> $           1.785,00</t>
+  </si>
+  <si>
+    <t> $                446,25</t>
+  </si>
+  <si>
+    <t>DLCH MILKAUT CLASICO CAMPO 395X                  </t>
+  </si>
+  <si>
+    <t> $           3.998,75</t>
+  </si>
+  <si>
+    <t> $           3.199,00</t>
+  </si>
+  <si>
+    <t> $                799,75</t>
+  </si>
+  <si>
+    <t>FIAM RECREO JAM COCIDO X KG                      </t>
+  </si>
+  <si>
+    <t> $        13.000,00</t>
+  </si>
+  <si>
+    <t> $                            -  </t>
+  </si>
+  <si>
+    <t>destacado</t>
+  </si>
+  <si>
+    <t>FIQU TREGAR CREMOSO X KG                         </t>
+  </si>
+  <si>
+    <t> $        11.990,00</t>
+  </si>
+  <si>
+    <t>GALS L.PROVIDENCIA 303X                          </t>
+  </si>
+  <si>
+    <t> $           1.561,25</t>
+  </si>
+  <si>
+    <t> $           1.249,00</t>
+  </si>
+  <si>
+    <t> $                312,25</t>
+  </si>
+  <si>
+    <t>LUAT TREGAR DESC T.BRIK 1X                       </t>
+  </si>
+  <si>
+    <t> $           2.248,75</t>
+  </si>
+  <si>
+    <t> $           1.799,00</t>
+  </si>
+  <si>
+    <t> $                449,75</t>
+  </si>
+  <si>
+    <t>LUAT TREGAR ENT T.BRIK 1X                        </t>
+  </si>
+  <si>
+    <t>PAPE FOFINHO PREMIUM D/H 100% 12X30X             </t>
+  </si>
+  <si>
+    <t> $           8.486,25</t>
+  </si>
+  <si>
+    <t> $           6.789,00</t>
+  </si>
+  <si>
+    <t> $           1.697,25</t>
+  </si>
+  <si>
+    <t>PAPE ELEGANTE H/S BCO 6X30X                      </t>
+  </si>
+  <si>
+    <t> $           3.312,50</t>
+  </si>
+  <si>
+    <t> $           2.650,00</t>
+  </si>
+  <si>
+    <t> $                662,50</t>
+  </si>
+  <si>
+    <t>ROLL COC ELEGANTE 50 PANOS 3X                    </t>
+  </si>
+  <si>
+    <t> $           2.343,75</t>
+  </si>
+  <si>
+    <t> $           1.875,00</t>
+  </si>
+  <si>
+    <t> $                468,75</t>
+  </si>
+  <si>
+    <t>YERB ROMANCE 500X                                </t>
+  </si>
+  <si>
+    <t> $           1.961,25</t>
+  </si>
+  <si>
+    <t> $           1.569,00</t>
+  </si>
+  <si>
+    <t> $                392,25</t>
+  </si>
+  <si>
+    <t>DETC MAGISTRAL ULTR LIMON 300X                   </t>
+  </si>
+  <si>
+    <t> $           2.486,25</t>
+  </si>
+  <si>
+    <t> $           1.989,00</t>
+  </si>
+  <si>
+    <t> $                497,25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;$&quot;_-;\-* #,##0.00\ &quot;$&quot;_-;_-* &quot;-&quot;??\ &quot;$&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
     <numFmt numFmtId="166" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5628,8 +5965,20 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5648,8 +5997,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -5699,13 +6054,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5944,148 +6341,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="3" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="40">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="26">
     <dxf>
       <font>
         <b val="0"/>
@@ -6397,14 +6702,65 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
       </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6506,62 +6862,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -6576,7 +6876,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{019ABB55-38CE-48A1-9BE5-DB0F31272943}" name="COMBOS" displayName="COMBOS" ref="A1:L104" totalsRowShown="0" headerRowDxfId="39" dataDxfId="11" headerRowBorderDxfId="38" tableBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{019ABB55-38CE-48A1-9BE5-DB0F31272943}" name="COMBOS" displayName="COMBOS" ref="A1:L104" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
   <autoFilter ref="A1:L104" xr:uid="{019ABB55-38CE-48A1-9BE5-DB0F31272943}">
     <filterColumn colId="7">
       <customFilters>
@@ -6588,18 +6888,18 @@
     <sortCondition ref="D1:D104"/>
   </sortState>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{D6BF27D7-B642-4DD0-AF71-251C385C6189}" name="COD_INT2" dataDxfId="23"/>
-    <tableColumn id="46" xr3:uid="{274A329A-2BB7-4D43-ACE2-09561E1F8231}" name="COD_PRO3" dataDxfId="22"/>
-    <tableColumn id="39" xr3:uid="{C67028AA-4B16-4240-A66F-9CAB766847C2}" name="SKU4" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{30E1B30F-DAE1-4849-8E0D-D73F8D72408E}" name="DESCRIPCION_ARTICULOS5" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{FAC3902E-481B-4616-9678-5E812867F701}" name="PRECIO6" dataDxfId="19" dataCellStyle="Millares"/>
-    <tableColumn id="4" xr3:uid="{B1922F06-AC51-4D09-8D82-45A4B453A1F2}" name="OFERTA7" dataDxfId="18" dataCellStyle="Millares"/>
-    <tableColumn id="5" xr3:uid="{8B8DF407-23B3-4A49-BDAB-D73F7BDF4C6A}" name="AHORRO8" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{B7DDB594-DB65-4653-BF38-E25F7F705A81}" name="DESDE" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{DBD4BF50-10C8-4ED1-B460-B5494924B31B}" name="HASTA" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{04EDB530-DAC2-4CCD-AB37-51C41175023A}" name="SUCURSAL" dataDxfId="14"/>
-    <tableColumn id="40" xr3:uid="{17C2DF41-D87D-439A-9992-D58832C17C27}" name="PROVEEDOR1" dataDxfId="13"/>
-    <tableColumn id="41" xr3:uid="{FD10D271-4162-467A-9481-FEB5ABC139CE}" name="PROVEEDOR2" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{D6BF27D7-B642-4DD0-AF71-251C385C6189}" name="COD_INT2" dataDxfId="11"/>
+    <tableColumn id="46" xr3:uid="{274A329A-2BB7-4D43-ACE2-09561E1F8231}" name="COD_PRO3" dataDxfId="10"/>
+    <tableColumn id="39" xr3:uid="{C67028AA-4B16-4240-A66F-9CAB766847C2}" name="SKU4" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{30E1B30F-DAE1-4849-8E0D-D73F8D72408E}" name="DESCRIPCION_ARTICULOS5" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{FAC3902E-481B-4616-9678-5E812867F701}" name="PRECIO6" dataDxfId="7" dataCellStyle="Millares"/>
+    <tableColumn id="4" xr3:uid="{B1922F06-AC51-4D09-8D82-45A4B453A1F2}" name="OFERTA7" dataDxfId="6" dataCellStyle="Millares"/>
+    <tableColumn id="5" xr3:uid="{8B8DF407-23B3-4A49-BDAB-D73F7BDF4C6A}" name="AHORRO8" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{B7DDB594-DB65-4653-BF38-E25F7F705A81}" name="DESDE" dataDxfId="4"/>
+    <tableColumn id="12" xr3:uid="{DBD4BF50-10C8-4ED1-B460-B5494924B31B}" name="HASTA" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{04EDB530-DAC2-4CCD-AB37-51C41175023A}" name="SUCURSAL" dataDxfId="2"/>
+    <tableColumn id="40" xr3:uid="{17C2DF41-D87D-439A-9992-D58832C17C27}" name="PROVEEDOR1" dataDxfId="1"/>
+    <tableColumn id="41" xr3:uid="{FD10D271-4162-467A-9481-FEB5ABC139CE}" name="PROVEEDOR2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6902,7 +7202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BDA83FB-36F5-4F27-8307-22D458931910}">
-  <dimension ref="A1:O1145"/>
+  <dimension ref="A1:O1175"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
@@ -54398,7 +54698,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="1145" spans="1:13">
+    <row r="1145" spans="1:13" ht="15.75" thickBot="1">
       <c r="A1145" s="79">
         <v>666313</v>
       </c>
@@ -54437,6 +54737,1146 @@
       </c>
       <c r="M1145" s="79" t="s">
         <v>827</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A1146" s="104">
+        <v>8466</v>
+      </c>
+      <c r="B1146" s="105" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1146" s="104">
+        <v>7796039001639</v>
+      </c>
+      <c r="D1146" s="106" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E1146" s="107" t="s">
+        <v>1852</v>
+      </c>
+      <c r="F1146" s="107" t="s">
+        <v>1853</v>
+      </c>
+      <c r="G1146" s="108" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H1146" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1146" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1146" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1146" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1146" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:13" ht="24.75" thickBot="1">
+      <c r="A1147" s="104">
+        <v>12379</v>
+      </c>
+      <c r="B1147" s="105">
+        <v>30616</v>
+      </c>
+      <c r="C1147" s="104">
+        <v>7791885001208</v>
+      </c>
+      <c r="D1147" s="111" t="s">
+        <v>1855</v>
+      </c>
+      <c r="E1147" s="107" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F1147" s="107" t="s">
+        <v>1857</v>
+      </c>
+      <c r="G1147" s="108" t="s">
+        <v>1858</v>
+      </c>
+      <c r="H1147" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1147" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1147" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1147" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1147" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:13" ht="24.75" thickBot="1">
+      <c r="A1148" s="104">
+        <v>12380</v>
+      </c>
+      <c r="B1148" s="105">
+        <v>30617</v>
+      </c>
+      <c r="C1148" s="104">
+        <v>7791885001550</v>
+      </c>
+      <c r="D1148" s="111" t="s">
+        <v>1859</v>
+      </c>
+      <c r="E1148" s="107" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F1148" s="107" t="s">
+        <v>1857</v>
+      </c>
+      <c r="G1148" s="108" t="s">
+        <v>1858</v>
+      </c>
+      <c r="H1148" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1148" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1148" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1148" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1148" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A1149" s="104">
+        <v>5584</v>
+      </c>
+      <c r="B1149" s="105">
+        <v>13873</v>
+      </c>
+      <c r="C1149" s="104">
+        <v>7790580660000</v>
+      </c>
+      <c r="D1149" s="111" t="s">
+        <v>1860</v>
+      </c>
+      <c r="E1149" s="107" t="s">
+        <v>1861</v>
+      </c>
+      <c r="F1149" s="107" t="s">
+        <v>1862</v>
+      </c>
+      <c r="G1149" s="108" t="s">
+        <v>1863</v>
+      </c>
+      <c r="H1149" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1149" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1149" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1149" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1149" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A1150" s="104">
+        <v>18186</v>
+      </c>
+      <c r="B1150" s="105" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1150" s="104">
+        <v>7797237000110</v>
+      </c>
+      <c r="D1150" s="111" t="s">
+        <v>1864</v>
+      </c>
+      <c r="E1150" s="107" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F1150" s="107" t="s">
+        <v>1866</v>
+      </c>
+      <c r="G1150" s="108" t="s">
+        <v>1867</v>
+      </c>
+      <c r="H1150" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1150" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1150" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1150" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1150" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A1151" s="104">
+        <v>101429</v>
+      </c>
+      <c r="B1151" s="105">
+        <v>50011</v>
+      </c>
+      <c r="C1151" s="104">
+        <v>7790503198450</v>
+      </c>
+      <c r="D1151" s="111" t="s">
+        <v>1868</v>
+      </c>
+      <c r="E1151" s="107" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F1151" s="107" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G1151" s="108" t="s">
+        <v>1871</v>
+      </c>
+      <c r="H1151" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1151" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1151" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1151" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1151" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A1152" s="104">
+        <v>660710</v>
+      </c>
+      <c r="B1152" s="105">
+        <v>7001</v>
+      </c>
+      <c r="C1152" s="104">
+        <v>7790387070019</v>
+      </c>
+      <c r="D1152" s="111" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E1152" s="107" t="s">
+        <v>1873</v>
+      </c>
+      <c r="F1152" s="107" t="s">
+        <v>1874</v>
+      </c>
+      <c r="G1152" s="108" t="s">
+        <v>1875</v>
+      </c>
+      <c r="H1152" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1152" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1152" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1152" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1152" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1153" s="104">
+        <v>18184</v>
+      </c>
+      <c r="B1153" s="105" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1153" s="104">
+        <v>7797237000028</v>
+      </c>
+      <c r="D1153" s="111" t="s">
+        <v>1876</v>
+      </c>
+      <c r="E1153" s="107" t="s">
+        <v>1877</v>
+      </c>
+      <c r="F1153" s="107" t="s">
+        <v>1878</v>
+      </c>
+      <c r="G1153" s="108" t="s">
+        <v>1879</v>
+      </c>
+      <c r="H1153" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1153" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1153" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1153" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1153" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1154" s="104">
+        <v>19637</v>
+      </c>
+      <c r="B1154" s="105">
+        <v>32031</v>
+      </c>
+      <c r="C1154" s="104">
+        <v>7790070320315</v>
+      </c>
+      <c r="D1154" s="111" t="s">
+        <v>1880</v>
+      </c>
+      <c r="E1154" s="107" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F1154" s="107" t="s">
+        <v>1882</v>
+      </c>
+      <c r="G1154" s="108" t="s">
+        <v>1883</v>
+      </c>
+      <c r="H1154" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1154" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1154" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1154" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1154" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:12" ht="24.75" thickBot="1">
+      <c r="A1155" s="104">
+        <v>19639</v>
+      </c>
+      <c r="B1155" s="105">
+        <v>32032</v>
+      </c>
+      <c r="C1155" s="104">
+        <v>7790070320322</v>
+      </c>
+      <c r="D1155" s="111" t="s">
+        <v>1884</v>
+      </c>
+      <c r="E1155" s="107" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F1155" s="107" t="s">
+        <v>1882</v>
+      </c>
+      <c r="G1155" s="108" t="s">
+        <v>1883</v>
+      </c>
+      <c r="H1155" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1155" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1155" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1155" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1155" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1156" s="104">
+        <v>19638</v>
+      </c>
+      <c r="B1156" s="105">
+        <v>32030</v>
+      </c>
+      <c r="C1156" s="104">
+        <v>7790070320308</v>
+      </c>
+      <c r="D1156" s="111" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E1156" s="107" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F1156" s="107" t="s">
+        <v>1882</v>
+      </c>
+      <c r="G1156" s="108" t="s">
+        <v>1883</v>
+      </c>
+      <c r="H1156" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1156" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1156" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1156" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1156" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1157" s="104">
+        <v>19641</v>
+      </c>
+      <c r="B1157" s="105">
+        <v>32029</v>
+      </c>
+      <c r="C1157" s="104">
+        <v>7790070320292</v>
+      </c>
+      <c r="D1157" s="111" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E1157" s="107" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F1157" s="107" t="s">
+        <v>1882</v>
+      </c>
+      <c r="G1157" s="108" t="s">
+        <v>1883</v>
+      </c>
+      <c r="H1157" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1157" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1157" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1157" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1157" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1158" s="104">
+        <v>19640</v>
+      </c>
+      <c r="B1158" s="105">
+        <v>32028</v>
+      </c>
+      <c r="C1158" s="104">
+        <v>7790070320285</v>
+      </c>
+      <c r="D1158" s="111" t="s">
+        <v>1887</v>
+      </c>
+      <c r="E1158" s="107" t="s">
+        <v>1881</v>
+      </c>
+      <c r="F1158" s="107" t="s">
+        <v>1882</v>
+      </c>
+      <c r="G1158" s="108" t="s">
+        <v>1883</v>
+      </c>
+      <c r="H1158" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1158" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1158" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1158" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1158" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1159" s="104">
+        <v>825</v>
+      </c>
+      <c r="B1159" s="105">
+        <v>5443</v>
+      </c>
+      <c r="C1159" s="104">
+        <v>7798156760062</v>
+      </c>
+      <c r="D1159" s="111" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E1159" s="107" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F1159" s="107" t="s">
+        <v>1890</v>
+      </c>
+      <c r="G1159" s="108" t="s">
+        <v>1891</v>
+      </c>
+      <c r="H1159" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1159" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1159" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1159" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1159" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:12" ht="24.75" thickBot="1">
+      <c r="A1160" s="104">
+        <v>4526</v>
+      </c>
+      <c r="B1160" s="105">
+        <v>5444</v>
+      </c>
+      <c r="C1160" s="104">
+        <v>7798156760024</v>
+      </c>
+      <c r="D1160" s="111" t="s">
+        <v>1892</v>
+      </c>
+      <c r="E1160" s="107" t="s">
+        <v>1893</v>
+      </c>
+      <c r="F1160" s="107" t="s">
+        <v>1894</v>
+      </c>
+      <c r="G1160" s="108" t="s">
+        <v>1895</v>
+      </c>
+      <c r="H1160" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1160" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1160" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1160" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1160" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1161" s="104">
+        <v>7458</v>
+      </c>
+      <c r="B1161" s="105" t="s">
+        <v>1850</v>
+      </c>
+      <c r="C1161" s="104">
+        <v>7798141971381</v>
+      </c>
+      <c r="D1161" s="111" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E1161" s="107" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F1161" s="107" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G1161" s="108" t="s">
+        <v>1871</v>
+      </c>
+      <c r="H1161" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1161" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1161" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1161" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1161" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:12" ht="24.75" thickBot="1">
+      <c r="A1162" s="104">
+        <v>660821</v>
+      </c>
+      <c r="B1162" s="105">
+        <v>12589756</v>
+      </c>
+      <c r="C1162" s="104">
+        <v>7613287953155</v>
+      </c>
+      <c r="D1162" s="111" t="s">
+        <v>1897</v>
+      </c>
+      <c r="E1162" s="107" t="s">
+        <v>1898</v>
+      </c>
+      <c r="F1162" s="107" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G1162" s="108" t="s">
+        <v>1861</v>
+      </c>
+      <c r="H1162" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1162" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1162" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1162" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1162" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:12" ht="24.75" thickBot="1">
+      <c r="A1163" s="104">
+        <v>660828</v>
+      </c>
+      <c r="B1163" s="105">
+        <v>12589762</v>
+      </c>
+      <c r="C1163" s="104">
+        <v>7613287953452</v>
+      </c>
+      <c r="D1163" s="111" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E1163" s="107" t="s">
+        <v>1898</v>
+      </c>
+      <c r="F1163" s="107" t="s">
+        <v>1899</v>
+      </c>
+      <c r="G1163" s="108" t="s">
+        <v>1861</v>
+      </c>
+      <c r="H1163" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1163" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1163" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1163" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1163" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1164" s="104">
+        <v>8213</v>
+      </c>
+      <c r="B1164" s="105">
+        <v>24683</v>
+      </c>
+      <c r="C1164" s="104">
+        <v>7793147118822</v>
+      </c>
+      <c r="D1164" s="111" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E1164" s="107" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F1164" s="107" t="s">
+        <v>1903</v>
+      </c>
+      <c r="G1164" s="108" t="s">
+        <v>1904</v>
+      </c>
+      <c r="H1164" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1164" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1164" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1164" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1164" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:12" ht="24.75" thickBot="1">
+      <c r="A1165" s="104">
+        <v>661619</v>
+      </c>
+      <c r="B1165" s="105">
+        <v>6303</v>
+      </c>
+      <c r="C1165" s="104">
+        <v>7794820902493</v>
+      </c>
+      <c r="D1165" s="111" t="s">
+        <v>1905</v>
+      </c>
+      <c r="E1165" s="107" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F1165" s="107" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G1165" s="108" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H1165" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1165" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1165" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1165" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1165" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:12" ht="24.75" thickBot="1">
+      <c r="A1166" s="104">
+        <v>3781</v>
+      </c>
+      <c r="B1166" s="105">
+        <v>12101</v>
+      </c>
+      <c r="C1166" s="104">
+        <v>2003781000000</v>
+      </c>
+      <c r="D1166" s="111" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1166" s="107" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F1166" s="107" t="s">
+        <v>1910</v>
+      </c>
+      <c r="G1166" s="108" t="s">
+        <v>1911</v>
+      </c>
+      <c r="H1166" s="109">
+        <v>0</v>
+      </c>
+      <c r="I1166" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1166" s="105" t="s">
+        <v>1912</v>
+      </c>
+      <c r="K1166" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1166" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1167" s="104">
+        <v>2422</v>
+      </c>
+      <c r="B1167" s="105">
+        <v>9</v>
+      </c>
+      <c r="C1167" s="104">
+        <v>2002422000000</v>
+      </c>
+      <c r="D1167" s="111" t="s">
+        <v>1913</v>
+      </c>
+      <c r="E1167" s="107" t="s">
+        <v>1914</v>
+      </c>
+      <c r="F1167" s="107" t="s">
+        <v>1914</v>
+      </c>
+      <c r="G1167" s="108" t="s">
+        <v>1911</v>
+      </c>
+      <c r="H1167" s="109">
+        <v>0</v>
+      </c>
+      <c r="I1167" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1167" s="105" t="s">
+        <v>1912</v>
+      </c>
+      <c r="K1167" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1167" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1168" s="104">
+        <v>18818</v>
+      </c>
+      <c r="B1168" s="105">
+        <v>0</v>
+      </c>
+      <c r="C1168" s="104">
+        <v>7798141972401</v>
+      </c>
+      <c r="D1168" s="111" t="s">
+        <v>1915</v>
+      </c>
+      <c r="E1168" s="107" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F1168" s="107" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G1168" s="108" t="s">
+        <v>1918</v>
+      </c>
+      <c r="H1168" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1168" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1168" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1168" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1168" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1169" s="104">
+        <v>8612</v>
+      </c>
+      <c r="B1169" s="105">
+        <v>1686</v>
+      </c>
+      <c r="C1169" s="104">
+        <v>7793913001839</v>
+      </c>
+      <c r="D1169" s="111" t="s">
+        <v>1919</v>
+      </c>
+      <c r="E1169" s="107" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F1169" s="107" t="s">
+        <v>1921</v>
+      </c>
+      <c r="G1169" s="108" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H1169" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1169" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1169" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1169" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1169" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1170" s="104">
+        <v>8610</v>
+      </c>
+      <c r="B1170" s="105">
+        <v>1685</v>
+      </c>
+      <c r="C1170" s="104">
+        <v>7793913001822</v>
+      </c>
+      <c r="D1170" s="111" t="s">
+        <v>1923</v>
+      </c>
+      <c r="E1170" s="107" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F1170" s="107" t="s">
+        <v>1921</v>
+      </c>
+      <c r="G1170" s="108" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H1170" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1170" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1170" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1170" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1170" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:12" ht="24.75" thickBot="1">
+      <c r="A1171" s="104">
+        <v>665981</v>
+      </c>
+      <c r="B1171" s="105">
+        <v>1346</v>
+      </c>
+      <c r="C1171" s="104">
+        <v>7896053410223</v>
+      </c>
+      <c r="D1171" s="111" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E1171" s="107" t="s">
+        <v>1925</v>
+      </c>
+      <c r="F1171" s="107" t="s">
+        <v>1926</v>
+      </c>
+      <c r="G1171" s="108" t="s">
+        <v>1927</v>
+      </c>
+      <c r="H1171" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1171" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1171" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1171" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1171" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:12" ht="24.75" thickBot="1">
+      <c r="A1172" s="104">
+        <v>13828</v>
+      </c>
+      <c r="B1172" s="105">
+        <v>904</v>
+      </c>
+      <c r="C1172" s="104">
+        <v>7793344904150</v>
+      </c>
+      <c r="D1172" s="111" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E1172" s="107" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F1172" s="107" t="s">
+        <v>1930</v>
+      </c>
+      <c r="G1172" s="108" t="s">
+        <v>1931</v>
+      </c>
+      <c r="H1172" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1172" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1172" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1172" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1172" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:12" ht="24.75" thickBot="1">
+      <c r="A1173" s="104">
+        <v>13813</v>
+      </c>
+      <c r="B1173" s="105">
+        <v>927</v>
+      </c>
+      <c r="C1173" s="104">
+        <v>7793344904013</v>
+      </c>
+      <c r="D1173" s="111" t="s">
+        <v>1932</v>
+      </c>
+      <c r="E1173" s="107" t="s">
+        <v>1933</v>
+      </c>
+      <c r="F1173" s="107" t="s">
+        <v>1934</v>
+      </c>
+      <c r="G1173" s="108" t="s">
+        <v>1935</v>
+      </c>
+      <c r="H1173" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1173" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1173" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1173" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1173" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A1174" s="104">
+        <v>2482</v>
+      </c>
+      <c r="B1174" s="105">
+        <v>11004</v>
+      </c>
+      <c r="C1174" s="104">
+        <v>7790802000010</v>
+      </c>
+      <c r="D1174" s="111" t="s">
+        <v>1936</v>
+      </c>
+      <c r="E1174" s="107" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F1174" s="107" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G1174" s="108" t="s">
+        <v>1939</v>
+      </c>
+      <c r="H1174" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1174" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1174" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1174" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1174" s="110">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:12" ht="24.75" thickBot="1">
+      <c r="A1175" s="104">
+        <v>4845</v>
+      </c>
+      <c r="B1175" s="105">
+        <v>9549506</v>
+      </c>
+      <c r="C1175" s="104">
+        <v>7590002018149</v>
+      </c>
+      <c r="D1175" s="111" t="s">
+        <v>1940</v>
+      </c>
+      <c r="E1175" s="107" t="s">
+        <v>1941</v>
+      </c>
+      <c r="F1175" s="107" t="s">
+        <v>1942</v>
+      </c>
+      <c r="G1175" s="108" t="s">
+        <v>1943</v>
+      </c>
+      <c r="H1175" s="109">
+        <v>0.2</v>
+      </c>
+      <c r="I1175" s="105" t="s">
+        <v>575</v>
+      </c>
+      <c r="J1175" s="105" t="s">
+        <v>527</v>
+      </c>
+      <c r="K1175" s="110">
+        <v>46177</v>
+      </c>
+      <c r="L1175" s="110">
+        <v>46203</v>
       </c>
     </row>
   </sheetData>
@@ -57688,10 +59128,10 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="C1:D1 A1">
-    <cfRule type="duplicateValues" dxfId="27" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -57699,7 +59139,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26ABB468-DF74-4389-8976-348A738DC311}">
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
@@ -60253,7 +61693,7 @@
         <v>8051.02</v>
       </c>
       <c r="F67" s="45">
-        <f>+E67-G67</f>
+        <f t="shared" ref="F67:F73" si="0">+E67-G67</f>
         <v>3550.8940000000002</v>
       </c>
       <c r="G67" s="45">
@@ -60293,7 +61733,7 @@
         <v>8355.52</v>
       </c>
       <c r="F68" s="45">
-        <f>+E68-G68</f>
+        <f t="shared" si="0"/>
         <v>3855.3940000000002</v>
       </c>
       <c r="G68" s="45">
@@ -60333,7 +61773,7 @@
         <v>6850.8899999999994</v>
       </c>
       <c r="F69" s="45">
-        <f>+E69-G69</f>
+        <f t="shared" si="0"/>
         <v>3550.8899999999994</v>
       </c>
       <c r="G69" s="45">
@@ -60373,7 +61813,7 @@
         <v>6032.9</v>
       </c>
       <c r="F70" s="45">
-        <f>+E70-G70</f>
+        <f t="shared" si="0"/>
         <v>2732.8999999999996</v>
       </c>
       <c r="G70" s="45">
@@ -60412,7 +61852,7 @@
         <v>12513.93</v>
       </c>
       <c r="F71" s="45">
-        <f>+E71-G71</f>
+        <f t="shared" si="0"/>
         <v>9213.93</v>
       </c>
       <c r="G71" s="45">
@@ -60451,7 +61891,7 @@
         <v>12513.93</v>
       </c>
       <c r="F72" s="45">
-        <f>+E72-G72</f>
+        <f t="shared" si="0"/>
         <v>9213.93</v>
       </c>
       <c r="G72" s="45">
@@ -60490,7 +61930,7 @@
         <v>11787.03</v>
       </c>
       <c r="F73" s="45">
-        <f>+E73-G73</f>
+        <f t="shared" si="0"/>
         <v>8487.0300000000007</v>
       </c>
       <c r="G73" s="45">
@@ -60989,7 +62429,7 @@
         <v>13482.77</v>
       </c>
       <c r="F86" s="45">
-        <f>+E86-G86</f>
+        <f t="shared" ref="F86:F91" si="1">+E86-G86</f>
         <v>10182.77</v>
       </c>
       <c r="G86" s="45">
@@ -61028,7 +62468,7 @@
         <v>14498.87</v>
       </c>
       <c r="F87" s="45">
-        <f>+E87-G87</f>
+        <f t="shared" si="1"/>
         <v>11198.87</v>
       </c>
       <c r="G87" s="45">
@@ -61067,7 +62507,7 @@
         <v>14498.87</v>
       </c>
       <c r="F88" s="45">
-        <f>+E88-G88</f>
+        <f t="shared" si="1"/>
         <v>11198.87</v>
       </c>
       <c r="G88" s="45">
@@ -61107,7 +62547,7 @@
         <v>14498.87</v>
       </c>
       <c r="F89" s="45">
-        <f>+E89-G89</f>
+        <f t="shared" si="1"/>
         <v>11198.87</v>
       </c>
       <c r="G89" s="45">
@@ -61147,7 +62587,7 @@
         <v>14498.87</v>
       </c>
       <c r="F90" s="45">
-        <f>+E90-G90</f>
+        <f t="shared" si="1"/>
         <v>11198.87</v>
       </c>
       <c r="G90" s="45">
@@ -61186,7 +62626,7 @@
         <v>14498.87</v>
       </c>
       <c r="F91" s="45">
-        <f>+E91-G91</f>
+        <f t="shared" si="1"/>
         <v>11198.87</v>
       </c>
       <c r="G91" s="45">
@@ -61227,26 +62667,138 @@
     <row r="94" spans="1:13" hidden="1"/>
     <row r="95" spans="1:13" hidden="1"/>
     <row r="96" spans="1:13" hidden="1"/>
-    <row r="97" hidden="1"/>
-    <row r="98" hidden="1"/>
-    <row r="99" hidden="1"/>
-    <row r="100" hidden="1"/>
-    <row r="101" hidden="1"/>
-    <row r="102" hidden="1"/>
-    <row r="103" hidden="1"/>
-    <row r="104" hidden="1"/>
+    <row r="97" spans="1:12" hidden="1"/>
+    <row r="98" spans="1:12" hidden="1"/>
+    <row r="99" spans="1:12" hidden="1"/>
+    <row r="100" spans="1:12" hidden="1"/>
+    <row r="101" spans="1:12" hidden="1"/>
+    <row r="102" spans="1:12" hidden="1"/>
+    <row r="103" spans="1:12" hidden="1"/>
+    <row r="104" spans="1:12" hidden="1"/>
+    <row r="105" spans="1:12" customFormat="1" ht="15">
+      <c r="A105" s="98" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B105" s="98"/>
+      <c r="C105" s="98"/>
+      <c r="D105" s="98" t="s">
+        <v>1833</v>
+      </c>
+      <c r="E105" s="99" t="s">
+        <v>1834</v>
+      </c>
+      <c r="F105" s="99" t="s">
+        <v>1835</v>
+      </c>
+      <c r="G105" s="99" t="s">
+        <v>1836</v>
+      </c>
+      <c r="H105" s="100">
+        <v>46176</v>
+      </c>
+      <c r="I105" s="100">
+        <v>46203</v>
+      </c>
+      <c r="J105" s="100"/>
+      <c r="K105" s="98"/>
+      <c r="L105" s="98"/>
+    </row>
+    <row r="106" spans="1:12" customFormat="1" ht="15">
+      <c r="A106" s="98" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B106" s="98"/>
+      <c r="C106" s="98"/>
+      <c r="D106" s="98" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E106" s="99" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F106" s="99" t="s">
+        <v>1840</v>
+      </c>
+      <c r="G106" s="99" t="s">
+        <v>1841</v>
+      </c>
+      <c r="H106" s="100">
+        <v>46176</v>
+      </c>
+      <c r="I106" s="100">
+        <v>46203</v>
+      </c>
+      <c r="J106" s="100"/>
+      <c r="K106" s="98"/>
+      <c r="L106" s="98"/>
+    </row>
+    <row r="107" spans="1:12" customFormat="1" ht="15">
+      <c r="A107" s="98" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B107" s="98"/>
+      <c r="C107" s="98"/>
+      <c r="D107" s="98" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E107" s="99" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F107" s="99" t="s">
+        <v>1845</v>
+      </c>
+      <c r="G107" s="99" t="s">
+        <v>1836</v>
+      </c>
+      <c r="H107" s="100">
+        <v>46176</v>
+      </c>
+      <c r="I107" s="100">
+        <v>46203</v>
+      </c>
+      <c r="J107" s="100"/>
+      <c r="K107" s="98"/>
+      <c r="L107" s="98"/>
+    </row>
+    <row r="108" spans="1:12" customFormat="1" ht="15">
+      <c r="A108" s="101" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B108" s="101"/>
+      <c r="C108" s="101"/>
+      <c r="D108" s="101" t="s">
+        <v>1847</v>
+      </c>
+      <c r="E108" s="102" t="s">
+        <v>1848</v>
+      </c>
+      <c r="F108" s="102" t="s">
+        <v>1849</v>
+      </c>
+      <c r="G108" s="102" t="s">
+        <v>1836</v>
+      </c>
+      <c r="H108" s="103">
+        <v>46176</v>
+      </c>
+      <c r="I108" s="103">
+        <v>46203</v>
+      </c>
+      <c r="J108" s="103"/>
+      <c r="K108" s="101"/>
+      <c r="L108" s="101"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="C1:D1 A1">
-    <cfRule type="duplicateValues" dxfId="10" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1 A106:XFD1048576 N2:XFD105 A2:M104">
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+  <conditionalFormatting sqref="A109:XFD1048576 A1:XFD104">
+    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:L104">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/padron de ofertas.xlsx
+++ b/padron de ofertas.xlsx
@@ -46133,3329 +46133,3422 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26ABB468-DF74-4389-8976-348A738DC311}">
-  <dimension ref="A1:K128"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr defaultColWidth="11.43359375" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.10546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.01953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.12890625" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.0859375" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.22265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.28125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.01171875" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.0234375" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.05859375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.0234375" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.43359375" style="7"/>
+    <col min="2" max="2" width="12.10546875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="25.01953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.12890625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.0859375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.22265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.01171875" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.0234375" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.05859375" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.0234375" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="11.43359375" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="68" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:12" s="68" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A1" s="65" t="s">
         <v>536</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B1" s="65"/>
+      <c r="C1" s="69" t="s">
         <v>328</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="D1" s="65" t="s">
         <v>329</v>
       </c>
-      <c r="D1" s="66" t="s">
+      <c r="E1" s="66" t="s">
         <v>330</v>
       </c>
-      <c r="E1" s="66" t="s">
+      <c r="F1" s="66" t="s">
         <v>331</v>
       </c>
-      <c r="F1" s="66" t="s">
+      <c r="G1" s="66" t="s">
         <v>332</v>
       </c>
-      <c r="G1" s="67" t="s">
+      <c r="H1" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="67" t="s">
+      <c r="I1" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="J1" s="65" t="s">
         <v>333</v>
       </c>
-      <c r="J1" s="65" t="s">
+      <c r="K1" s="65" t="s">
         <v>334</v>
       </c>
-      <c r="K1" s="65" t="s">
+      <c r="L1" s="65" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A2" s="11" t="s">
         <v>539</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="D2" s="13">
+      <c r="E2" s="13">
         <v>18014.100999999999</v>
       </c>
-      <c r="E2" s="13">
+      <c r="F2" s="13">
         <v>13213.92</v>
       </c>
-      <c r="F2" s="56">
-        <f t="shared" ref="F2:F33" si="0">+E2-D2</f>
+      <c r="G2" s="56">
+        <f t="shared" ref="G2:G33" si="0">+F2-E2</f>
         <v>-4800.1809999999987</v>
       </c>
-      <c r="G2" s="12">
+      <c r="H2" s="12">
         <v>46204</v>
       </c>
-      <c r="H2" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J2" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3" s="11" t="s">
         <v>540</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="11"/>
+      <c r="C3" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="D3" s="13">
+      <c r="E3" s="13">
         <v>24600.181</v>
       </c>
-      <c r="E3" s="13">
+      <c r="F3" s="13">
         <v>19800</v>
       </c>
-      <c r="F3" s="56">
+      <c r="G3" s="56">
         <f t="shared" si="0"/>
         <v>-4800.1810000000005</v>
       </c>
-      <c r="G3" s="12">
+      <c r="H3" s="12">
         <v>46204</v>
       </c>
-      <c r="H3" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A4" s="11" t="s">
         <v>541</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11" t="s">
         <v>537</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>538</v>
       </c>
-      <c r="D4" s="13">
+      <c r="E4" s="13">
         <f>19900+4800.18</f>
         <v>24700.18</v>
       </c>
-      <c r="E4" s="13">
+      <c r="F4" s="13">
         <v>19900</v>
       </c>
-      <c r="F4" s="56">
+      <c r="G4" s="56">
         <f t="shared" si="0"/>
         <v>-4800.18</v>
       </c>
-      <c r="G4" s="12">
+      <c r="H4" s="12">
         <v>46204</v>
       </c>
-      <c r="H4" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="K4" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="L4" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A5" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="D5" s="13">
+      <c r="E5" s="13">
         <v>11654.242999999999</v>
       </c>
-      <c r="E5" s="13">
+      <c r="F5" s="13">
         <v>6854.0619999999999</v>
       </c>
-      <c r="F5" s="56">
+      <c r="G5" s="56">
         <f t="shared" si="0"/>
         <v>-4800.1809999999987</v>
       </c>
-      <c r="G5" s="12">
+      <c r="H5" s="12">
         <v>46204</v>
       </c>
-      <c r="H5" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="K5" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="L5" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A6" s="11" t="s">
         <v>543</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="D6" s="13">
+      <c r="E6" s="13">
         <v>14803.411</v>
       </c>
-      <c r="E6" s="13">
+      <c r="F6" s="13">
         <v>10003.23</v>
       </c>
-      <c r="F6" s="56">
+      <c r="G6" s="56">
         <f t="shared" si="0"/>
         <v>-4800.1810000000005</v>
       </c>
-      <c r="G6" s="12">
+      <c r="H6" s="12">
         <v>46204</v>
       </c>
-      <c r="H6" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="K6" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="L6" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A7" s="11" t="s">
         <v>544</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="11"/>
+      <c r="C7" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="D7" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="D7" s="13">
+      <c r="E7" s="13">
         <v>31317.651000000002</v>
       </c>
-      <c r="E7" s="13">
+      <c r="F7" s="13">
         <v>26517.47</v>
       </c>
-      <c r="F7" s="56">
+      <c r="G7" s="56">
         <f t="shared" si="0"/>
         <v>-4800.1810000000005</v>
       </c>
-      <c r="G7" s="12">
+      <c r="H7" s="12">
         <v>46204</v>
       </c>
-      <c r="H7" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I7" s="11" t="s">
+      <c r="I7" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="K7" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K7" s="11" t="s">
+      <c r="L7" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A8" s="11" t="s">
         <v>545</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11" t="s">
         <v>376</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="D8" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="D8" s="13">
+      <c r="E8" s="13">
         <v>10913.759999999998</v>
       </c>
-      <c r="E8" s="13">
+      <c r="F8" s="13">
         <v>6113.5789999999997</v>
       </c>
-      <c r="F8" s="56">
+      <c r="G8" s="56">
         <f t="shared" si="0"/>
         <v>-4800.1809999999987</v>
       </c>
-      <c r="G8" s="12">
+      <c r="H8" s="12">
         <v>46204</v>
       </c>
-      <c r="H8" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="K8" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="L8" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A9" s="11" t="s">
         <v>546</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11" t="s">
         <v>454</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="D9" s="11" t="s">
         <v>455</v>
       </c>
-      <c r="D9" s="13">
+      <c r="E9" s="13">
         <v>15802.710999999999</v>
       </c>
-      <c r="E9" s="13">
+      <c r="F9" s="13">
         <v>11002.53</v>
       </c>
-      <c r="F9" s="56">
+      <c r="G9" s="56">
         <f t="shared" si="0"/>
         <v>-4800.1809999999987</v>
       </c>
-      <c r="G9" s="12">
+      <c r="H9" s="12">
         <v>46204</v>
       </c>
-      <c r="H9" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="K9" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="L9" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A10" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="D10" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="D10" s="13">
+      <c r="E10" s="13">
         <v>13349.124</v>
       </c>
-      <c r="E10" s="13">
+      <c r="F10" s="13">
         <v>8749</v>
       </c>
-      <c r="F10" s="56">
+      <c r="G10" s="56">
         <f t="shared" si="0"/>
         <v>-4600.1239999999998</v>
       </c>
-      <c r="G10" s="12">
+      <c r="H10" s="12">
         <v>46204</v>
       </c>
-      <c r="H10" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="K10" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="L10" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A11" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="D11" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="D11" s="13">
+      <c r="E11" s="13">
         <v>10449.124</v>
       </c>
-      <c r="E11" s="13">
+      <c r="F11" s="13">
         <v>5849</v>
       </c>
-      <c r="F11" s="56">
+      <c r="G11" s="56">
         <f t="shared" si="0"/>
         <v>-4600.1239999999998</v>
       </c>
-      <c r="G11" s="12">
+      <c r="H11" s="12">
         <v>46204</v>
       </c>
-      <c r="H11" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="K11" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="L11" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A12" s="11" t="s">
         <v>549</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="11"/>
+      <c r="C12" s="11" t="s">
         <v>396</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="D12" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="D12" s="13">
+      <c r="E12" s="13">
         <v>8151.0209999999997</v>
       </c>
-      <c r="E12" s="13">
+      <c r="F12" s="13">
         <v>3550.8969999999999</v>
       </c>
-      <c r="F12" s="56">
+      <c r="G12" s="56">
         <f t="shared" si="0"/>
         <v>-4600.1239999999998</v>
       </c>
-      <c r="G12" s="12">
+      <c r="H12" s="12">
         <v>46204</v>
       </c>
-      <c r="H12" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J12" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="K12" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="L12" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A13" s="11" t="s">
         <v>550</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="11"/>
+      <c r="C13" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="D13" s="11" t="s">
         <v>535</v>
       </c>
-      <c r="D13" s="13">
+      <c r="E13" s="13">
         <v>8455.5149999999994</v>
       </c>
-      <c r="E13" s="13">
+      <c r="F13" s="13">
         <v>3855.3910000000001</v>
       </c>
-      <c r="F13" s="56">
+      <c r="G13" s="56">
         <f t="shared" si="0"/>
         <v>-4600.1239999999998</v>
       </c>
-      <c r="G13" s="12">
+      <c r="H13" s="12">
         <v>46204</v>
       </c>
-      <c r="H13" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J13" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="11"/>
+      <c r="L13" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A14" s="11" t="s">
         <v>551</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="D14" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="D14" s="13">
+      <c r="E14" s="13">
         <v>12118.106</v>
       </c>
-      <c r="E14" s="13">
+      <c r="F14" s="13">
         <v>8615.0159999999996</v>
       </c>
-      <c r="F14" s="56">
+      <c r="G14" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G14" s="12">
+      <c r="H14" s="12">
         <v>46204</v>
       </c>
-      <c r="H14" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I14" s="11" t="s">
+      <c r="I14" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J14" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="K14" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="L14" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A15" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="D15" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="D15" s="13">
+      <c r="E15" s="13">
         <v>16494.78</v>
       </c>
-      <c r="E15" s="13">
+      <c r="F15" s="13">
         <v>12991.69</v>
       </c>
-      <c r="F15" s="56">
+      <c r="G15" s="56">
         <f t="shared" si="0"/>
         <v>-3503.0899999999983</v>
       </c>
-      <c r="G15" s="12">
+      <c r="H15" s="12">
         <v>46204</v>
       </c>
-      <c r="H15" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I15" s="11" t="s">
+      <c r="I15" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J15" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="K15" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="L15" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A16" s="11" t="s">
         <v>553</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="D16" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="D16" s="13">
+      <c r="E16" s="13">
         <v>38370.399999999994</v>
       </c>
-      <c r="E16" s="13">
+      <c r="F16" s="13">
         <v>34867.31</v>
       </c>
-      <c r="F16" s="56">
+      <c r="G16" s="56">
         <f t="shared" si="0"/>
         <v>-3503.0899999999965</v>
       </c>
-      <c r="G16" s="12">
+      <c r="H16" s="12">
         <v>46204</v>
       </c>
-      <c r="H16" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="K16" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="L16" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A17" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="11"/>
+      <c r="C17" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="D17" s="13">
+      <c r="E17" s="13">
         <v>20304.009999999998</v>
       </c>
-      <c r="E17" s="13">
+      <c r="F17" s="13">
         <v>16800.919999999998</v>
       </c>
-      <c r="F17" s="56">
+      <c r="G17" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G17" s="12">
+      <c r="H17" s="12">
         <v>46204</v>
       </c>
-      <c r="H17" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="K17" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="L17" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A18" s="11" t="s">
         <v>555</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="D18" s="13">
+      <c r="E18" s="13">
         <v>11925.623</v>
       </c>
-      <c r="E18" s="13">
+      <c r="F18" s="13">
         <v>8422.5329999999994</v>
       </c>
-      <c r="F18" s="56">
+      <c r="G18" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G18" s="12">
+      <c r="H18" s="12">
         <v>46204</v>
       </c>
-      <c r="H18" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I18" s="11" t="s">
+      <c r="I18" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="K18" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="L18" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A19" s="11" t="s">
         <v>556</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="D19" s="11" t="s">
         <v>399</v>
       </c>
-      <c r="D19" s="13">
+      <c r="E19" s="13">
         <v>9540.4650000000001</v>
       </c>
-      <c r="E19" s="13">
+      <c r="F19" s="13">
         <v>6037.375</v>
       </c>
-      <c r="F19" s="56">
+      <c r="G19" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G19" s="12">
+      <c r="H19" s="12">
         <v>46204</v>
       </c>
-      <c r="H19" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J19" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="K19" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="L19" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A20" s="11" t="s">
         <v>557</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11" t="s">
         <v>401</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="D20" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="D20" s="13">
+      <c r="E20" s="13">
         <v>34216.03</v>
       </c>
-      <c r="E20" s="13">
+      <c r="F20" s="13">
         <v>30712.94</v>
       </c>
-      <c r="F20" s="56">
+      <c r="G20" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G20" s="12">
+      <c r="H20" s="12">
         <v>46204</v>
       </c>
-      <c r="H20" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I20" s="11" t="s">
+      <c r="I20" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J20" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="K20" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="L20" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A21" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="11"/>
+      <c r="C21" s="11" t="s">
         <v>407</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="D21" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="D21" s="13">
+      <c r="E21" s="13">
         <v>16988.09</v>
       </c>
-      <c r="E21" s="13">
+      <c r="F21" s="13">
         <v>13485</v>
       </c>
-      <c r="F21" s="56">
+      <c r="G21" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G21" s="12">
+      <c r="H21" s="12">
         <v>46204</v>
       </c>
-      <c r="H21" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I21" s="11" t="s">
+      <c r="I21" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="K21" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="L21" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A22" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="D22" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="D22" s="13">
+      <c r="E22" s="13">
         <v>14523.09</v>
       </c>
-      <c r="E22" s="13">
+      <c r="F22" s="13">
         <v>11020</v>
       </c>
-      <c r="F22" s="56">
+      <c r="G22" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G22" s="12">
+      <c r="H22" s="12">
         <v>46204</v>
       </c>
-      <c r="H22" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I22" s="11" t="s">
+      <c r="I22" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J22" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="K22" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="L22" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A23" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="11"/>
+      <c r="C23" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="D23" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="D23" s="13">
+      <c r="E23" s="13">
         <v>14523.09</v>
       </c>
-      <c r="E23" s="13">
+      <c r="F23" s="13">
         <v>11020</v>
       </c>
-      <c r="F23" s="56">
+      <c r="G23" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G23" s="12">
+      <c r="H23" s="12">
         <v>46204</v>
       </c>
-      <c r="H23" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I23" s="11" t="s">
+      <c r="I23" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J23" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="K23" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="L23" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A24" s="11" t="s">
         <v>561</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="11"/>
+      <c r="C24" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="D24" s="11" t="s">
         <v>415</v>
       </c>
-      <c r="D24" s="13">
+      <c r="E24" s="13">
         <v>14523.09</v>
       </c>
-      <c r="E24" s="13">
+      <c r="F24" s="13">
         <v>11020</v>
       </c>
-      <c r="F24" s="56">
+      <c r="G24" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G24" s="12">
+      <c r="H24" s="12">
         <v>46204</v>
       </c>
-      <c r="H24" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J24" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="K24" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="L24" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A25" s="11" t="s">
         <v>562</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="11"/>
+      <c r="C25" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="D25" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="D25" s="13">
+      <c r="E25" s="13">
         <v>14523.09</v>
       </c>
-      <c r="E25" s="13">
+      <c r="F25" s="13">
         <v>11020</v>
       </c>
-      <c r="F25" s="56">
+      <c r="G25" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G25" s="12">
+      <c r="H25" s="12">
         <v>46204</v>
       </c>
-      <c r="H25" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J25" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="K25" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="L25" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A26" s="11" t="s">
         <v>563</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="11"/>
+      <c r="C26" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="D26" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="D26" s="13">
+      <c r="E26" s="13">
         <v>45364.28</v>
       </c>
-      <c r="E26" s="13">
+      <c r="F26" s="13">
         <v>41861.19</v>
       </c>
-      <c r="F26" s="56">
+      <c r="G26" s="56">
         <f t="shared" si="0"/>
         <v>-3503.0899999999965</v>
       </c>
-      <c r="G26" s="12">
+      <c r="H26" s="12">
         <v>46204</v>
       </c>
-      <c r="H26" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J26" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="K26" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="L26" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A27" s="11" t="s">
         <v>564</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="11"/>
+      <c r="C27" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="D27" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="D27" s="13">
+      <c r="E27" s="13">
         <v>19378.38</v>
       </c>
-      <c r="E27" s="13">
+      <c r="F27" s="13">
         <v>15875.29</v>
       </c>
-      <c r="F27" s="56">
+      <c r="G27" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G27" s="12">
+      <c r="H27" s="12">
         <v>46204</v>
       </c>
-      <c r="H27" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J27" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="K27" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="L27" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A28" s="11" t="s">
         <v>565</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="11"/>
+      <c r="C28" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="D28" s="11" t="s">
         <v>429</v>
       </c>
-      <c r="D28" s="13">
+      <c r="E28" s="13">
         <v>86588.33</v>
       </c>
-      <c r="E28" s="13">
+      <c r="F28" s="13">
         <v>83085.240000000005</v>
       </c>
-      <c r="F28" s="56">
+      <c r="G28" s="56">
         <f t="shared" si="0"/>
         <v>-3503.0899999999965</v>
       </c>
-      <c r="G28" s="12">
+      <c r="H28" s="12">
         <v>46204</v>
       </c>
-      <c r="H28" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J28" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="K28" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="L28" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A29" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="11"/>
+      <c r="C29" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="D29" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="D29" s="13">
+      <c r="E29" s="13">
         <v>40023.25</v>
       </c>
-      <c r="E29" s="13">
+      <c r="F29" s="13">
         <v>36520.160000000003</v>
       </c>
-      <c r="F29" s="56">
+      <c r="G29" s="56">
         <f t="shared" si="0"/>
         <v>-3503.0899999999965</v>
       </c>
-      <c r="G29" s="12">
+      <c r="H29" s="12">
         <v>46204</v>
       </c>
-      <c r="H29" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J29" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="K29" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="L29" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A30" s="11" t="s">
         <v>567</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11" t="s">
         <v>432</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="D30" s="11" t="s">
         <v>433</v>
       </c>
-      <c r="D30" s="13">
+      <c r="E30" s="13">
         <v>40024.899999999994</v>
       </c>
-      <c r="E30" s="13">
+      <c r="F30" s="13">
         <v>36521.81</v>
       </c>
-      <c r="F30" s="56">
+      <c r="G30" s="56">
         <f t="shared" si="0"/>
         <v>-3503.0899999999965</v>
       </c>
-      <c r="G30" s="12">
+      <c r="H30" s="12">
         <v>46204</v>
       </c>
-      <c r="H30" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J30" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="K30" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K30" s="11" t="s">
+      <c r="L30" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A31" s="11" t="s">
         <v>568</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="D31" s="11" t="s">
         <v>435</v>
       </c>
-      <c r="D31" s="13">
+      <c r="E31" s="13">
         <v>66592.710000000006</v>
       </c>
-      <c r="E31" s="13">
+      <c r="F31" s="13">
         <v>63089.62</v>
       </c>
-      <c r="F31" s="56">
+      <c r="G31" s="56">
         <f t="shared" si="0"/>
         <v>-3503.0900000000038</v>
       </c>
-      <c r="G31" s="12">
+      <c r="H31" s="12">
         <v>46204</v>
       </c>
-      <c r="H31" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I31" s="11" t="s">
+      <c r="I31" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J31" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J31" s="11" t="s">
+      <c r="K31" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K31" s="11" t="s">
+      <c r="L31" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A32" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="11"/>
+      <c r="C32" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="D32" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="D32" s="13">
+      <c r="E32" s="13">
         <v>11870.654</v>
       </c>
-      <c r="E32" s="13">
+      <c r="F32" s="13">
         <v>8367.5640000000003</v>
       </c>
-      <c r="F32" s="56">
+      <c r="G32" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G32" s="12">
+      <c r="H32" s="12">
         <v>46204</v>
       </c>
-      <c r="H32" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J32" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J32" s="11" t="s">
+      <c r="K32" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K32" s="11" t="s">
+      <c r="L32" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A33" s="11" t="s">
         <v>570</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="11" t="s">
         <v>448</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="D33" s="11" t="s">
         <v>449</v>
       </c>
-      <c r="D33" s="13">
+      <c r="E33" s="13">
         <v>15564.14</v>
       </c>
-      <c r="E33" s="13">
+      <c r="F33" s="13">
         <v>12061.05</v>
       </c>
-      <c r="F33" s="56">
+      <c r="G33" s="56">
         <f t="shared" si="0"/>
         <v>-3503.09</v>
       </c>
-      <c r="G33" s="12">
+      <c r="H33" s="12">
         <v>46204</v>
       </c>
-      <c r="H33" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J33" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J33" s="11" t="s">
+      <c r="K33" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K33" s="11" t="s">
+      <c r="L33" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A34" s="11" t="s">
         <v>571</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="11"/>
+      <c r="C34" s="11" t="s">
         <v>450</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="D34" s="11" t="s">
         <v>451</v>
       </c>
-      <c r="D34" s="13">
+      <c r="E34" s="13">
         <v>13073.098</v>
       </c>
-      <c r="E34" s="13">
+      <c r="F34" s="13">
         <v>9570.0079999999998</v>
       </c>
-      <c r="F34" s="56">
-        <f t="shared" ref="F34:F65" si="1">+E34-D34</f>
+      <c r="G34" s="56">
+        <f t="shared" ref="G34:G65" si="1">+F34-E34</f>
         <v>-3503.09</v>
       </c>
-      <c r="G34" s="12">
+      <c r="H34" s="12">
         <v>46204</v>
       </c>
-      <c r="H34" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J34" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J34" s="11" t="s">
+      <c r="K34" s="11" t="s">
         <v>409</v>
       </c>
-      <c r="K34" s="11" t="s">
+      <c r="L34" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A35" s="11" t="s">
         <v>572</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="11"/>
+      <c r="C35" s="11" t="s">
         <v>452</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="D35" s="11" t="s">
         <v>453</v>
       </c>
-      <c r="D35" s="13">
+      <c r="E35" s="13">
         <v>40024.899999999994</v>
       </c>
-      <c r="E35" s="13">
+      <c r="F35" s="13">
         <v>36521.81</v>
       </c>
-      <c r="F35" s="56">
+      <c r="G35" s="56">
         <f t="shared" si="1"/>
         <v>-3503.0899999999965</v>
       </c>
-      <c r="G35" s="12">
+      <c r="H35" s="12">
         <v>46204</v>
       </c>
-      <c r="H35" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I35" s="11" t="s">
+      <c r="I35" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J35" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J35" s="11" t="s">
+      <c r="K35" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K35" s="11" t="s">
+      <c r="L35" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A36" s="11" t="s">
         <v>573</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="11"/>
+      <c r="C36" s="11" t="s">
         <v>460</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="D36" s="11" t="s">
         <v>461</v>
       </c>
-      <c r="D36" s="13">
+      <c r="E36" s="13">
         <v>76060.800000000003</v>
       </c>
-      <c r="E36" s="13">
+      <c r="F36" s="13">
         <v>72557.710000000006</v>
       </c>
-      <c r="F36" s="56">
+      <c r="G36" s="56">
         <f t="shared" si="1"/>
         <v>-3503.0899999999965</v>
       </c>
-      <c r="G36" s="12">
+      <c r="H36" s="12">
         <v>46204</v>
       </c>
-      <c r="H36" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I36" s="11" t="s">
+      <c r="I36" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J36" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J36" s="11" t="s">
+      <c r="K36" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K36" s="11" t="s">
+      <c r="L36" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A37" s="11" t="s">
         <v>574</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="11"/>
+      <c r="C37" s="11" t="s">
         <v>462</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="D37" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D37" s="13">
+      <c r="E37" s="13">
         <v>45366.960000000006</v>
       </c>
-      <c r="E37" s="13">
+      <c r="F37" s="13">
         <v>41863.870000000003</v>
       </c>
-      <c r="F37" s="56">
+      <c r="G37" s="56">
         <f t="shared" si="1"/>
         <v>-3503.0900000000038</v>
       </c>
-      <c r="G37" s="12">
+      <c r="H37" s="12">
         <v>46204</v>
       </c>
-      <c r="H37" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J37" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J37" s="11" t="s">
+      <c r="K37" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="K37" s="11" t="s">
+      <c r="L37" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A38" s="11" t="s">
         <v>575</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="11"/>
+      <c r="C38" s="11" t="s">
         <v>466</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="D38" s="11" t="s">
         <v>467</v>
       </c>
-      <c r="D38" s="13">
+      <c r="E38" s="13">
         <v>16135.49</v>
       </c>
-      <c r="E38" s="13">
+      <c r="F38" s="13">
         <v>12632.4</v>
       </c>
-      <c r="F38" s="56">
+      <c r="G38" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G38" s="12">
+      <c r="H38" s="12">
         <v>46204</v>
       </c>
-      <c r="H38" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I38" s="11" t="s">
+      <c r="I38" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J38" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="K38" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="K38" s="11" t="s">
+      <c r="L38" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A39" s="11" t="s">
         <v>576</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="11"/>
+      <c r="C39" s="11" t="s">
         <v>474</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="D39" s="11" t="s">
         <v>475</v>
       </c>
-      <c r="D39" s="13">
+      <c r="E39" s="13">
         <v>14258.31</v>
       </c>
-      <c r="E39" s="13">
+      <c r="F39" s="13">
         <v>10755.22</v>
       </c>
-      <c r="F39" s="56">
+      <c r="G39" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G39" s="12">
+      <c r="H39" s="12">
         <v>46204</v>
       </c>
-      <c r="H39" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I39" s="11" t="s">
+      <c r="I39" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J39" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J39" s="11" t="s">
+      <c r="K39" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K39" s="11" t="s">
+      <c r="L39" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A40" s="11" t="s">
         <v>577</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="11"/>
+      <c r="C40" s="11" t="s">
         <v>478</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="D40" s="11" t="s">
         <v>479</v>
       </c>
-      <c r="D40" s="13">
+      <c r="E40" s="13">
         <v>13070.73</v>
       </c>
-      <c r="E40" s="13">
+      <c r="F40" s="13">
         <v>9567.64</v>
       </c>
-      <c r="F40" s="56">
+      <c r="G40" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G40" s="12">
+      <c r="H40" s="12">
         <v>46204</v>
       </c>
-      <c r="H40" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I40" s="11" t="s">
+      <c r="I40" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J40" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J40" s="11" t="s">
+      <c r="K40" s="11" t="s">
         <v>480</v>
       </c>
-      <c r="K40" s="11" t="s">
+      <c r="L40" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A41" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="11"/>
+      <c r="C41" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="D41" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="D41" s="13">
+      <c r="E41" s="13">
         <v>28076.76</v>
       </c>
-      <c r="E41" s="13">
+      <c r="F41" s="13">
         <v>24573.67</v>
       </c>
-      <c r="F41" s="56">
+      <c r="G41" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G41" s="12">
+      <c r="H41" s="12">
         <v>46204</v>
       </c>
-      <c r="H41" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I41" s="11" t="s">
+      <c r="I41" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J41" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J41" s="11" t="s">
+      <c r="K41" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="K41" s="11" t="s">
+      <c r="L41" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A42" s="11" t="s">
         <v>579</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="11"/>
+      <c r="C42" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="D42" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="D42" s="13">
+      <c r="E42" s="13">
         <v>20260.11</v>
       </c>
-      <c r="E42" s="13">
+      <c r="F42" s="13">
         <v>16757.02</v>
       </c>
-      <c r="F42" s="56">
+      <c r="G42" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G42" s="12">
+      <c r="H42" s="12">
         <v>46204</v>
       </c>
-      <c r="H42" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I42" s="11" t="s">
+      <c r="I42" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J42" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J42" s="11" t="s">
+      <c r="K42" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K42" s="11" t="s">
+      <c r="L42" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A43" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="11"/>
+      <c r="C43" s="11" t="s">
         <v>490</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="D43" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="D43" s="13">
+      <c r="E43" s="13">
         <v>16711.21</v>
       </c>
-      <c r="E43" s="13">
+      <c r="F43" s="13">
         <v>13208.12</v>
       </c>
-      <c r="F43" s="56">
+      <c r="G43" s="56">
         <f t="shared" si="1"/>
         <v>-3503.0899999999983</v>
       </c>
-      <c r="G43" s="12">
+      <c r="H43" s="12">
         <v>46204</v>
       </c>
-      <c r="H43" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I43" s="11" t="s">
+      <c r="I43" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J43" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J43" s="11" t="s">
+      <c r="K43" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K43" s="11" t="s">
+      <c r="L43" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A44" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="11"/>
+      <c r="C44" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="D44" s="11" t="s">
         <v>493</v>
       </c>
-      <c r="D44" s="13">
+      <c r="E44" s="13">
         <v>16711.21</v>
       </c>
-      <c r="E44" s="13">
+      <c r="F44" s="13">
         <v>13208.12</v>
       </c>
-      <c r="F44" s="56">
+      <c r="G44" s="56">
         <f t="shared" si="1"/>
         <v>-3503.0899999999983</v>
       </c>
-      <c r="G44" s="12">
+      <c r="H44" s="12">
         <v>46204</v>
       </c>
-      <c r="H44" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I44" s="11" t="s">
+      <c r="I44" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J44" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J44" s="11" t="s">
+      <c r="K44" s="11" t="s">
         <v>400</v>
       </c>
-      <c r="K44" s="11" t="s">
+      <c r="L44" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A45" s="11" t="s">
         <v>582</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="11"/>
+      <c r="C45" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="D45" s="11" t="s">
         <v>498</v>
       </c>
-      <c r="D45" s="13">
+      <c r="E45" s="13">
         <v>19017.599999999999</v>
       </c>
-      <c r="E45" s="13">
+      <c r="F45" s="13">
         <v>15514.51</v>
       </c>
-      <c r="F45" s="56">
+      <c r="G45" s="56">
         <f t="shared" si="1"/>
         <v>-3503.0899999999983</v>
       </c>
-      <c r="G45" s="12">
+      <c r="H45" s="12">
         <v>46204</v>
       </c>
-      <c r="H45" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I45" s="11" t="s">
+      <c r="I45" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J45" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J45" s="11" t="s">
+      <c r="K45" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="K45" s="11" t="s">
+      <c r="L45" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A46" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="11"/>
+      <c r="C46" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="D46" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="D46" s="13">
+      <c r="E46" s="13">
         <v>20304.009999999998</v>
       </c>
-      <c r="E46" s="13">
+      <c r="F46" s="13">
         <v>16800.919999999998</v>
       </c>
-      <c r="F46" s="56">
+      <c r="G46" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G46" s="12">
+      <c r="H46" s="12">
         <v>46204</v>
       </c>
-      <c r="H46" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I46" s="11" t="s">
+      <c r="I46" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J46" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J46" s="11" t="s">
+      <c r="K46" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="K46" s="11" t="s">
+      <c r="L46" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A47" s="11" t="s">
         <v>584</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="11"/>
+      <c r="C47" s="11" t="s">
         <v>503</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="D47" s="11" t="s">
         <v>504</v>
       </c>
-      <c r="D47" s="13">
+      <c r="E47" s="13">
         <v>20304.009999999998</v>
       </c>
-      <c r="E47" s="13">
+      <c r="F47" s="13">
         <v>16800.919999999998</v>
       </c>
-      <c r="F47" s="56">
+      <c r="G47" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G47" s="12">
+      <c r="H47" s="12">
         <v>46204</v>
       </c>
-      <c r="H47" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I47" s="11" t="s">
+      <c r="I47" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J47" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J47" s="11" t="s">
+      <c r="K47" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="K47" s="11" t="s">
+      <c r="L47" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A48" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="11"/>
+      <c r="C48" s="11" t="s">
         <v>505</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="D48" s="11" t="s">
         <v>506</v>
       </c>
-      <c r="D48" s="13">
+      <c r="E48" s="13">
         <v>20961.099999999999</v>
       </c>
-      <c r="E48" s="13">
+      <c r="F48" s="13">
         <v>17458.009999999998</v>
       </c>
-      <c r="F48" s="56">
+      <c r="G48" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G48" s="12">
+      <c r="H48" s="12">
         <v>46204</v>
       </c>
-      <c r="H48" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I48" s="11" t="s">
+      <c r="I48" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J48" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J48" s="11" t="s">
+      <c r="K48" s="11" t="s">
         <v>468</v>
       </c>
-      <c r="K48" s="11" t="s">
+      <c r="L48" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A49" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="11"/>
+      <c r="C49" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="D49" s="11" t="s">
         <v>508</v>
       </c>
-      <c r="D49" s="13">
+      <c r="E49" s="13">
         <v>70017.61</v>
       </c>
-      <c r="E49" s="13">
+      <c r="F49" s="13">
         <v>66514.52</v>
       </c>
-      <c r="F49" s="56">
+      <c r="G49" s="56">
         <f t="shared" si="1"/>
         <v>-3503.0899999999965</v>
       </c>
-      <c r="G49" s="12">
+      <c r="H49" s="12">
         <v>46204</v>
       </c>
-      <c r="H49" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I49" s="11" t="s">
+      <c r="I49" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J49" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J49" s="11" t="s">
+      <c r="K49" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="K49" s="11" t="s">
+      <c r="L49" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A50" s="11" t="s">
         <v>587</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="11"/>
+      <c r="C50" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="D50" s="11" t="s">
         <v>514</v>
       </c>
-      <c r="D50" s="13">
+      <c r="E50" s="13">
         <v>17287.169999999998</v>
       </c>
-      <c r="E50" s="13">
+      <c r="F50" s="13">
         <v>13784.08</v>
       </c>
-      <c r="F50" s="56">
+      <c r="G50" s="56">
         <f t="shared" si="1"/>
         <v>-3503.0899999999983</v>
       </c>
-      <c r="G50" s="12">
+      <c r="H50" s="12">
         <v>46204</v>
       </c>
-      <c r="H50" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I50" s="11" t="s">
+      <c r="I50" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J50" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J50" s="11" t="s">
+      <c r="K50" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="K50" s="11" t="s">
+      <c r="L50" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A51" s="11" t="s">
         <v>588</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="11"/>
+      <c r="C51" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="D51" s="11" t="s">
         <v>520</v>
       </c>
-      <c r="D51" s="13">
+      <c r="E51" s="13">
         <v>20847.09</v>
       </c>
-      <c r="E51" s="13">
+      <c r="F51" s="13">
         <v>17344</v>
       </c>
-      <c r="F51" s="56">
+      <c r="G51" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G51" s="12">
+      <c r="H51" s="12">
         <v>46204</v>
       </c>
-      <c r="H51" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I51" s="11" t="s">
+      <c r="I51" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J51" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J51" s="11" t="s">
+      <c r="K51" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="K51" s="11" t="s">
+      <c r="L51" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A52" s="11" t="s">
         <v>589</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="11"/>
+      <c r="C52" s="11" t="s">
         <v>521</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="D52" s="11" t="s">
         <v>522</v>
       </c>
-      <c r="D52" s="13">
+      <c r="E52" s="13">
         <v>11652.742</v>
       </c>
-      <c r="E52" s="13">
+      <c r="F52" s="13">
         <v>8149.652</v>
       </c>
-      <c r="F52" s="56">
+      <c r="G52" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G52" s="12">
+      <c r="H52" s="12">
         <v>46204</v>
       </c>
-      <c r="H52" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I52" s="11" t="s">
+      <c r="I52" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J52" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J52" s="11" t="s">
+      <c r="K52" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="K52" s="11" t="s">
+      <c r="L52" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A53" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="11"/>
+      <c r="C53" s="11" t="s">
         <v>523</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="D53" s="11" t="s">
         <v>524</v>
       </c>
-      <c r="D53" s="13">
+      <c r="E53" s="13">
         <v>11652.742</v>
       </c>
-      <c r="E53" s="13">
+      <c r="F53" s="13">
         <v>8149.652</v>
       </c>
-      <c r="F53" s="56">
+      <c r="G53" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G53" s="12">
+      <c r="H53" s="12">
         <v>46204</v>
       </c>
-      <c r="H53" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I53" s="11" t="s">
+      <c r="I53" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J53" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J53" s="11" t="s">
+      <c r="K53" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="K53" s="11" t="s">
+      <c r="L53" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A54" s="11" t="s">
         <v>591</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="11"/>
+      <c r="C54" s="11" t="s">
         <v>532</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="D54" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="D54" s="13">
+      <c r="E54" s="13">
         <v>20304.009999999998</v>
       </c>
-      <c r="E54" s="13">
+      <c r="F54" s="13">
         <v>16800.919999999998</v>
       </c>
-      <c r="F54" s="56">
+      <c r="G54" s="56">
         <f t="shared" si="1"/>
         <v>-3503.09</v>
       </c>
-      <c r="G54" s="12">
+      <c r="H54" s="12">
         <v>46204</v>
       </c>
-      <c r="H54" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I54" s="11" t="s">
+      <c r="I54" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J54" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J54" s="11" t="s">
+      <c r="K54" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="K54" s="11" t="s">
+      <c r="L54" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A55" s="11" t="s">
         <v>592</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="11"/>
+      <c r="C55" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="D55" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="D55" s="13">
+      <c r="E55" s="13">
         <v>13400.928</v>
       </c>
-      <c r="E55" s="13">
+      <c r="F55" s="13">
         <v>9900</v>
       </c>
-      <c r="F55" s="56">
+      <c r="G55" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G55" s="12">
+      <c r="H55" s="12">
         <v>46204</v>
       </c>
-      <c r="H55" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I55" s="11" t="s">
+      <c r="I55" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J55" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J55" s="11" t="s">
+      <c r="K55" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K55" s="11" t="s">
+      <c r="L55" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A56" s="11" t="s">
         <v>593</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="11"/>
+      <c r="C56" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="D56" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="D56" s="13">
+      <c r="E56" s="13">
         <v>7051.8249999999998</v>
       </c>
-      <c r="E56" s="13">
+      <c r="F56" s="13">
         <v>3550.8969999999999</v>
       </c>
-      <c r="F56" s="56">
+      <c r="G56" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G56" s="12">
+      <c r="H56" s="12">
         <v>46204</v>
       </c>
-      <c r="H56" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I56" s="11" t="s">
+      <c r="I56" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J56" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J56" s="11" t="s">
+      <c r="K56" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="K56" s="11" t="s">
+      <c r="L56" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A57" s="11" t="s">
         <v>594</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="11"/>
+      <c r="C57" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="D57" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="D57" s="13">
+      <c r="E57" s="13">
         <v>13683.698</v>
       </c>
-      <c r="E57" s="13">
+      <c r="F57" s="13">
         <v>10182.77</v>
       </c>
-      <c r="F57" s="56">
+      <c r="G57" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G57" s="12">
+      <c r="H57" s="12">
         <v>46204</v>
       </c>
-      <c r="H57" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I57" s="11" t="s">
+      <c r="I57" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J57" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J57" s="11" t="s">
+      <c r="K57" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="K57" s="11" t="s">
+      <c r="L57" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A58" s="11" t="s">
         <v>595</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="11"/>
+      <c r="C58" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="D58" s="11" t="s">
         <v>373</v>
       </c>
-      <c r="D58" s="13">
+      <c r="E58" s="13">
         <v>11987.954</v>
       </c>
-      <c r="E58" s="13">
+      <c r="F58" s="13">
         <v>8487.0259999999998</v>
       </c>
-      <c r="F58" s="56">
+      <c r="G58" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G58" s="12">
+      <c r="H58" s="12">
         <v>46204</v>
       </c>
-      <c r="H58" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I58" s="11" t="s">
+      <c r="I58" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J58" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J58" s="11" t="s">
+      <c r="K58" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K58" s="11" t="s">
+      <c r="L58" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A59" s="11" t="s">
         <v>596</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="11"/>
+      <c r="C59" s="11" t="s">
         <v>374</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="D59" s="11" t="s">
         <v>375</v>
       </c>
-      <c r="D59" s="13">
+      <c r="E59" s="13">
         <v>17320.928</v>
       </c>
-      <c r="E59" s="13">
+      <c r="F59" s="13">
         <v>13820</v>
       </c>
-      <c r="F59" s="56">
+      <c r="G59" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G59" s="12">
+      <c r="H59" s="12">
         <v>46204</v>
       </c>
-      <c r="H59" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I59" s="11" t="s">
+      <c r="I59" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J59" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J59" s="11" t="s">
+      <c r="K59" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K59" s="11" t="s">
+      <c r="L59" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A60" s="11" t="s">
         <v>597</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="11"/>
+      <c r="C60" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="D60" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="D60" s="13">
+      <c r="E60" s="13">
         <v>15261.328</v>
       </c>
-      <c r="E60" s="13">
+      <c r="F60" s="13">
         <v>11760.4</v>
       </c>
-      <c r="F60" s="56">
+      <c r="G60" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G60" s="12">
+      <c r="H60" s="12">
         <v>46204</v>
       </c>
-      <c r="H60" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I60" s="11" t="s">
+      <c r="I60" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J60" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J60" s="11" t="s">
+      <c r="K60" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K60" s="11" t="s">
+      <c r="L60" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A61" s="11" t="s">
         <v>598</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="11"/>
+      <c r="C61" s="11" t="s">
         <v>382</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="D61" s="11" t="s">
         <v>383</v>
       </c>
-      <c r="D61" s="13">
+      <c r="E61" s="13">
         <v>15060.928</v>
       </c>
-      <c r="E61" s="13">
+      <c r="F61" s="13">
         <v>11560</v>
       </c>
-      <c r="F61" s="56">
+      <c r="G61" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G61" s="12">
+      <c r="H61" s="12">
         <v>46204</v>
       </c>
-      <c r="H61" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I61" s="11" t="s">
+      <c r="I61" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J61" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J61" s="11" t="s">
+      <c r="K61" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K61" s="11" t="s">
+      <c r="L61" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A62" s="11" t="s">
         <v>599</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="11"/>
+      <c r="C62" s="11" t="s">
         <v>384</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="D62" s="11" t="s">
         <v>385</v>
       </c>
-      <c r="D62" s="13">
+      <c r="E62" s="13">
         <v>15060.928</v>
       </c>
-      <c r="E62" s="13">
+      <c r="F62" s="13">
         <v>11560</v>
       </c>
-      <c r="F62" s="56">
+      <c r="G62" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G62" s="12">
+      <c r="H62" s="12">
         <v>46204</v>
       </c>
-      <c r="H62" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I62" s="11" t="s">
+      <c r="I62" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J62" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J62" s="11" t="s">
+      <c r="K62" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K62" s="11" t="s">
+      <c r="L62" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A63" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="11"/>
+      <c r="C63" s="11" t="s">
         <v>386</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="D63" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="D63" s="13">
+      <c r="E63" s="13">
         <v>12440.491</v>
       </c>
-      <c r="E63" s="13">
+      <c r="F63" s="13">
         <v>8939.5630000000001</v>
       </c>
-      <c r="F63" s="56">
+      <c r="G63" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G63" s="12">
+      <c r="H63" s="12">
         <v>46204</v>
       </c>
-      <c r="H63" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I63" s="11" t="s">
+      <c r="I63" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J63" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J63" s="11" t="s">
+      <c r="K63" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K63" s="11" t="s">
+      <c r="L63" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A64" s="11" t="s">
         <v>601</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="11"/>
+      <c r="C64" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="D64" s="11" t="s">
         <v>389</v>
       </c>
-      <c r="D64" s="13">
+      <c r="E64" s="13">
         <v>14290.928</v>
       </c>
-      <c r="E64" s="13">
+      <c r="F64" s="13">
         <v>10790</v>
       </c>
-      <c r="F64" s="56">
+      <c r="G64" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G64" s="12">
+      <c r="H64" s="12">
         <v>46204</v>
       </c>
-      <c r="H64" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I64" s="11" t="s">
+      <c r="I64" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J64" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J64" s="11" t="s">
+      <c r="K64" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K64" s="11" t="s">
+      <c r="L64" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A65" s="11" t="s">
         <v>602</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="11"/>
+      <c r="C65" s="11" t="s">
         <v>390</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="D65" s="11" t="s">
         <v>391</v>
       </c>
-      <c r="D65" s="13">
+      <c r="E65" s="13">
         <v>14699.798000000001</v>
       </c>
-      <c r="E65" s="13">
+      <c r="F65" s="13">
         <v>11198.87</v>
       </c>
-      <c r="F65" s="56">
+      <c r="G65" s="56">
         <f t="shared" si="1"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G65" s="12">
+      <c r="H65" s="12">
         <v>46204</v>
       </c>
-      <c r="H65" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I65" s="11" t="s">
+      <c r="I65" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J65" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J65" s="11" t="s">
+      <c r="K65" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="K65" s="11" t="s">
+      <c r="L65" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A66" s="11" t="s">
         <v>603</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="11"/>
+      <c r="C66" s="11" t="s">
         <v>392</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="D66" s="11" t="s">
         <v>393</v>
       </c>
-      <c r="D66" s="13">
+      <c r="E66" s="13">
         <v>14699.798000000001</v>
       </c>
-      <c r="E66" s="13">
+      <c r="F66" s="13">
         <v>11198.87</v>
       </c>
-      <c r="F66" s="56">
-        <f t="shared" ref="F66:F92" si="2">+E66-D66</f>
+      <c r="G66" s="56">
+        <f t="shared" ref="G66:G92" si="2">+F66-E66</f>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G66" s="12">
+      <c r="H66" s="12">
         <v>46204</v>
       </c>
-      <c r="H66" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I66" s="11" t="s">
+      <c r="I66" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J66" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J66" s="11" t="s">
+      <c r="K66" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="K66" s="11" t="s">
+      <c r="L66" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A67" s="11" t="s">
         <v>604</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="11"/>
+      <c r="C67" s="11" t="s">
         <v>394</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="D67" s="11" t="s">
         <v>395</v>
       </c>
-      <c r="D67" s="13">
+      <c r="E67" s="13">
         <v>14699.798000000001</v>
       </c>
-      <c r="E67" s="13">
+      <c r="F67" s="13">
         <v>11198.87</v>
       </c>
-      <c r="F67" s="56">
+      <c r="G67" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G67" s="12">
+      <c r="H67" s="12">
         <v>46204</v>
       </c>
-      <c r="H67" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I67" s="11" t="s">
+      <c r="I67" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J67" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J67" s="11" t="s">
+      <c r="K67" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="K67" s="11" t="s">
+      <c r="L67" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A68" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="11"/>
+      <c r="C68" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="D68" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="D68" s="13">
+      <c r="E68" s="13">
         <v>16000.928</v>
       </c>
-      <c r="E68" s="13">
+      <c r="F68" s="13">
         <v>12500</v>
       </c>
-      <c r="F68" s="56">
+      <c r="G68" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G68" s="12">
+      <c r="H68" s="12">
         <v>46204</v>
       </c>
-      <c r="H68" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I68" s="11" t="s">
+      <c r="I68" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J68" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J68" s="11" t="s">
+      <c r="K68" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K68" s="11" t="s">
+      <c r="L68" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A69" s="11" t="s">
         <v>606</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="11"/>
+      <c r="C69" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="D69" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="D69" s="13">
+      <c r="E69" s="13">
         <v>11868.492</v>
       </c>
-      <c r="E69" s="13">
+      <c r="F69" s="13">
         <v>8367.5640000000003</v>
       </c>
-      <c r="F69" s="56">
+      <c r="G69" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G69" s="12">
+      <c r="H69" s="12">
         <v>46204</v>
       </c>
-      <c r="H69" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I69" s="11" t="s">
+      <c r="I69" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J69" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J69" s="11" t="s">
+      <c r="K69" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K69" s="11" t="s">
+      <c r="L69" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A70" s="11" t="s">
         <v>607</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="11"/>
+      <c r="C70" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="D70" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="D70" s="13">
+      <c r="E70" s="13">
         <v>15060.928</v>
       </c>
-      <c r="E70" s="13">
+      <c r="F70" s="13">
         <v>11560</v>
       </c>
-      <c r="F70" s="56">
+      <c r="G70" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G70" s="12">
+      <c r="H70" s="12">
         <v>46204</v>
       </c>
-      <c r="H70" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I70" s="11" t="s">
+      <c r="I70" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J70" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J70" s="11" t="s">
+      <c r="K70" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="L70" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A71" s="11" t="s">
         <v>608</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="11"/>
+      <c r="C71" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="D71" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="D71" s="13">
+      <c r="E71" s="13">
         <v>15060.928</v>
       </c>
-      <c r="E71" s="13">
+      <c r="F71" s="13">
         <v>11560</v>
       </c>
-      <c r="F71" s="56">
+      <c r="G71" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G71" s="12">
+      <c r="H71" s="12">
         <v>46204</v>
       </c>
-      <c r="H71" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I71" s="11" t="s">
+      <c r="I71" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J71" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J71" s="11" t="s">
+      <c r="K71" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K71" s="11" t="s">
+      <c r="L71" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A72" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="11"/>
+      <c r="C72" s="11" t="s">
         <v>422</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="D72" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="D72" s="13">
+      <c r="E72" s="13">
         <v>15060.928</v>
       </c>
-      <c r="E72" s="13">
+      <c r="F72" s="13">
         <v>11560</v>
       </c>
-      <c r="F72" s="56">
+      <c r="G72" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G72" s="12">
+      <c r="H72" s="12">
         <v>46204</v>
       </c>
-      <c r="H72" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I72" s="11" t="s">
+      <c r="I72" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J72" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J72" s="11" t="s">
+      <c r="K72" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K72" s="11" t="s">
+      <c r="L72" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A73" s="11" t="s">
         <v>610</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="11"/>
+      <c r="C73" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="D73" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="D73" s="13">
+      <c r="E73" s="13">
         <v>8802.023000000001</v>
       </c>
-      <c r="E73" s="13">
+      <c r="F73" s="13">
         <v>5301.0950000000003</v>
       </c>
-      <c r="F73" s="56">
+      <c r="G73" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9280000000008</v>
       </c>
-      <c r="G73" s="12">
+      <c r="H73" s="12">
         <v>46204</v>
       </c>
-      <c r="H73" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I73" s="11" t="s">
+      <c r="I73" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J73" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J73" s="11" t="s">
+      <c r="K73" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="K73" s="11" t="s">
+      <c r="L73" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A74" s="11" t="s">
         <v>611</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="11"/>
+      <c r="C74" s="11" t="s">
         <v>438</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="D74" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="D74" s="13">
+      <c r="E74" s="13">
         <v>12714.86</v>
       </c>
-      <c r="E74" s="13">
+      <c r="F74" s="13">
         <v>9213.9320000000007</v>
       </c>
-      <c r="F74" s="56">
+      <c r="G74" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G74" s="12">
+      <c r="H74" s="12">
         <v>46204</v>
       </c>
-      <c r="H74" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I74" s="11" t="s">
+      <c r="I74" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J74" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J74" s="11" t="s">
+      <c r="K74" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K74" s="11" t="s">
+      <c r="L74" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A75" s="11" t="s">
         <v>612</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="11"/>
+      <c r="C75" s="11" t="s">
         <v>440</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="D75" s="11" t="s">
         <v>441</v>
       </c>
-      <c r="D75" s="13">
+      <c r="E75" s="13">
         <v>10939.918</v>
       </c>
-      <c r="E75" s="13">
+      <c r="F75" s="13">
         <v>7438.99</v>
       </c>
-      <c r="F75" s="56">
+      <c r="G75" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G75" s="12">
+      <c r="H75" s="12">
         <v>46204</v>
       </c>
-      <c r="H75" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I75" s="11" t="s">
+      <c r="I75" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J75" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J75" s="11" t="s">
+      <c r="K75" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K75" s="11" t="s">
+      <c r="L75" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A76" s="11" t="s">
         <v>613</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="11"/>
+      <c r="C76" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="D76" s="11" t="s">
         <v>445</v>
       </c>
-      <c r="D76" s="13">
+      <c r="E76" s="13">
         <v>14699.798000000001</v>
       </c>
-      <c r="E76" s="13">
+      <c r="F76" s="13">
         <v>11198.87</v>
       </c>
-      <c r="F76" s="56">
+      <c r="G76" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G76" s="12">
+      <c r="H76" s="12">
         <v>46204</v>
       </c>
-      <c r="H76" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I76" s="11" t="s">
+      <c r="I76" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J76" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J76" s="11" t="s">
+      <c r="K76" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="K76" s="11" t="s">
+      <c r="L76" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A77" s="11" t="s">
         <v>614</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="11"/>
+      <c r="C77" s="11" t="s">
         <v>446</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="D77" s="11" t="s">
         <v>447</v>
       </c>
-      <c r="D77" s="13">
+      <c r="E77" s="13">
         <v>14699.798000000001</v>
       </c>
-      <c r="E77" s="13">
+      <c r="F77" s="13">
         <v>11198.87</v>
       </c>
-      <c r="F77" s="56">
+      <c r="G77" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G77" s="12">
+      <c r="H77" s="12">
         <v>46204</v>
       </c>
-      <c r="H77" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I77" s="11" t="s">
+      <c r="I77" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J77" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J77" s="11" t="s">
+      <c r="K77" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="K77" s="11" t="s">
+      <c r="L77" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A78" s="11" t="s">
         <v>615</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="11"/>
+      <c r="C78" s="11" t="s">
         <v>456</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="D78" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="D78" s="13">
+      <c r="E78" s="13">
         <v>12714.86</v>
       </c>
-      <c r="E78" s="13">
+      <c r="F78" s="13">
         <v>9213.9320000000007</v>
       </c>
-      <c r="F78" s="56">
+      <c r="G78" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G78" s="12">
+      <c r="H78" s="12">
         <v>46204</v>
       </c>
-      <c r="H78" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I78" s="11" t="s">
+      <c r="I78" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J78" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J78" s="11" t="s">
+      <c r="K78" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K78" s="11" t="s">
+      <c r="L78" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A79" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="11"/>
+      <c r="C79" s="11" t="s">
         <v>458</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="D79" s="11" t="s">
         <v>459</v>
       </c>
-      <c r="D79" s="13">
+      <c r="E79" s="13">
         <v>12714.86</v>
       </c>
-      <c r="E79" s="13">
+      <c r="F79" s="13">
         <v>9213.9320000000007</v>
       </c>
-      <c r="F79" s="56">
+      <c r="G79" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G79" s="12">
+      <c r="H79" s="12">
         <v>46204</v>
       </c>
-      <c r="H79" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I79" s="11" t="s">
+      <c r="I79" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J79" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J79" s="11" t="s">
+      <c r="K79" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K79" s="11" t="s">
+      <c r="L79" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A80" s="11" t="s">
         <v>617</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="11"/>
+      <c r="C80" s="11" t="s">
         <v>464</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="D80" s="11" t="s">
         <v>465</v>
       </c>
-      <c r="D80" s="13">
+      <c r="E80" s="13">
         <v>15880.928</v>
       </c>
-      <c r="E80" s="13">
+      <c r="F80" s="13">
         <v>12380</v>
       </c>
-      <c r="F80" s="56">
+      <c r="G80" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G80" s="12">
+      <c r="H80" s="12">
         <v>46204</v>
       </c>
-      <c r="H80" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I80" s="11" t="s">
+      <c r="I80" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J80" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J80" s="11" t="s">
+      <c r="K80" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K80" s="11" t="s">
+      <c r="L80" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A81" s="11" t="s">
         <v>618</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="11"/>
+      <c r="C81" s="11" t="s">
         <v>469</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="D81" s="11" t="s">
         <v>470</v>
       </c>
-      <c r="D81" s="13">
+      <c r="E81" s="13">
         <v>17275.928</v>
       </c>
-      <c r="E81" s="13">
+      <c r="F81" s="13">
         <v>13775</v>
       </c>
-      <c r="F81" s="56">
+      <c r="G81" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G81" s="12">
+      <c r="H81" s="12">
         <v>46204</v>
       </c>
-      <c r="H81" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I81" s="11" t="s">
+      <c r="I81" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J81" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J81" s="11" t="s">
+      <c r="K81" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="L81" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A82" s="11" t="s">
         <v>619</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="11"/>
+      <c r="C82" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="D82" s="11" t="s">
         <v>473</v>
       </c>
-      <c r="D82" s="13">
+      <c r="E82" s="13">
         <v>17275.928</v>
       </c>
-      <c r="E82" s="13">
+      <c r="F82" s="13">
         <v>13775</v>
       </c>
-      <c r="F82" s="56">
+      <c r="G82" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G82" s="12">
+      <c r="H82" s="12">
         <v>46204</v>
       </c>
-      <c r="H82" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I82" s="11" t="s">
+      <c r="I82" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J82" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J82" s="11" t="s">
+      <c r="K82" s="11" t="s">
         <v>471</v>
       </c>
-      <c r="K82" s="11" t="s">
+      <c r="L82" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A83" s="11" t="s">
         <v>620</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="11"/>
+      <c r="C83" s="11" t="s">
         <v>476</v>
       </c>
-      <c r="C83" s="11" t="s">
+      <c r="D83" s="11" t="s">
         <v>477</v>
       </c>
-      <c r="D83" s="13">
+      <c r="E83" s="13">
         <v>12714.86</v>
       </c>
-      <c r="E83" s="13">
+      <c r="F83" s="13">
         <v>9213.9320000000007</v>
       </c>
-      <c r="F83" s="56">
+      <c r="G83" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G83" s="12">
+      <c r="H83" s="12">
         <v>46204</v>
       </c>
-      <c r="H83" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I83" s="11" t="s">
+      <c r="I83" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J83" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J83" s="11" t="s">
+      <c r="K83" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K83" s="11" t="s">
+      <c r="L83" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A84" s="11" t="s">
         <v>621</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="11"/>
+      <c r="C84" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="D84" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="D84" s="13">
+      <c r="E84" s="13">
         <v>28074.597999999998</v>
       </c>
-      <c r="E84" s="13">
+      <c r="F84" s="13">
         <v>24573.67</v>
       </c>
-      <c r="F84" s="56">
+      <c r="G84" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G84" s="12">
+      <c r="H84" s="12">
         <v>46204</v>
       </c>
-      <c r="H84" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I84" s="11" t="s">
+      <c r="I84" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J84" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J84" s="11" t="s">
+      <c r="K84" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="K84" s="11" t="s">
+      <c r="L84" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A85" s="11" t="s">
         <v>622</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="11"/>
+      <c r="C85" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="C85" s="11" t="s">
+      <c r="D85" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="D85" s="13">
+      <c r="E85" s="13">
         <v>15060.928</v>
       </c>
-      <c r="E85" s="13">
+      <c r="F85" s="13">
         <v>11560</v>
       </c>
-      <c r="F85" s="56">
+      <c r="G85" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G85" s="12">
+      <c r="H85" s="12">
         <v>46204</v>
       </c>
-      <c r="H85" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I85" s="11" t="s">
+      <c r="I85" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J85" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J85" s="11" t="s">
+      <c r="K85" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K85" s="11" t="s">
+      <c r="L85" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="11" t="s">
         <v>623</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="11"/>
+      <c r="C86" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="D86" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="D86" s="13">
+      <c r="E86" s="13">
         <v>6233.83</v>
       </c>
-      <c r="E86" s="13">
+      <c r="F86" s="13">
         <v>2732.902</v>
       </c>
-      <c r="F86" s="56">
+      <c r="G86" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G86" s="12">
+      <c r="H86" s="12">
         <v>46204</v>
       </c>
-      <c r="H86" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I86" s="11" t="s">
+      <c r="I86" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J86" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J86" s="11" t="s">
+      <c r="K86" s="11" t="s">
         <v>496</v>
       </c>
-      <c r="K86" s="11" t="s">
+      <c r="L86" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A87" s="11" t="s">
         <v>624</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="11"/>
+      <c r="C87" s="11" t="s">
         <v>499</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="D87" s="11" t="s">
         <v>500</v>
       </c>
-      <c r="D87" s="13">
+      <c r="E87" s="13">
         <v>19986.207999999999</v>
       </c>
-      <c r="E87" s="13">
+      <c r="F87" s="13">
         <v>16485.28</v>
       </c>
-      <c r="F87" s="56">
+      <c r="G87" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G87" s="12">
+      <c r="H87" s="12">
         <v>46204</v>
       </c>
-      <c r="H87" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I87" s="11" t="s">
+      <c r="I87" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J87" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J87" s="11" t="s">
+      <c r="K87" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="K87" s="11" t="s">
+      <c r="L87" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A88" s="11" t="s">
         <v>625</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="11"/>
+      <c r="C88" s="11" t="s">
         <v>510</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="D88" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="D88" s="13">
+      <c r="E88" s="13">
         <v>21186.288</v>
       </c>
-      <c r="E88" s="13">
+      <c r="F88" s="13">
         <v>17685.36</v>
       </c>
-      <c r="F88" s="56">
+      <c r="G88" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G88" s="12">
+      <c r="H88" s="12">
         <v>46204</v>
       </c>
-      <c r="H88" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I88" s="11" t="s">
+      <c r="I88" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J88" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J88" s="11" t="s">
+      <c r="K88" s="11" t="s">
         <v>512</v>
       </c>
-      <c r="K88" s="11" t="s">
+      <c r="L88" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A89" s="11" t="s">
         <v>626</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="11"/>
+      <c r="C89" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="D89" s="11" t="s">
         <v>517</v>
       </c>
-      <c r="D89" s="13">
+      <c r="E89" s="13">
         <v>22400.918000000001</v>
       </c>
-      <c r="E89" s="13">
+      <c r="F89" s="13">
         <v>18899.990000000002</v>
       </c>
-      <c r="F89" s="56">
+      <c r="G89" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G89" s="12">
+      <c r="H89" s="12">
         <v>46204</v>
       </c>
-      <c r="H89" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I89" s="11" t="s">
+      <c r="I89" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J89" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J89" s="11" t="s">
+      <c r="K89" s="11" t="s">
         <v>518</v>
       </c>
-      <c r="K89" s="11" t="s">
+      <c r="L89" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A90" s="11" t="s">
         <v>627</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="11"/>
+      <c r="C90" s="11" t="s">
         <v>525</v>
       </c>
-      <c r="C90" s="11" t="s">
+      <c r="D90" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="D90" s="13">
+      <c r="E90" s="13">
         <v>15060.928</v>
       </c>
-      <c r="E90" s="13">
+      <c r="F90" s="13">
         <v>11560</v>
       </c>
-      <c r="F90" s="56">
+      <c r="G90" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G90" s="12">
+      <c r="H90" s="12">
         <v>46204</v>
       </c>
-      <c r="H90" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I90" s="11" t="s">
+      <c r="I90" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J90" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J90" s="11" t="s">
+      <c r="K90" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="K90" s="11" t="s">
+      <c r="L90" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A91" s="11" t="s">
         <v>628</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="11"/>
+      <c r="C91" s="11" t="s">
         <v>527</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="D91" s="11" t="s">
         <v>528</v>
       </c>
-      <c r="D91" s="13">
+      <c r="E91" s="13">
         <v>12714.86</v>
       </c>
-      <c r="E91" s="13">
+      <c r="F91" s="13">
         <v>9213.9320000000007</v>
       </c>
-      <c r="F91" s="56">
+      <c r="G91" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G91" s="12">
+      <c r="H91" s="12">
         <v>46204</v>
       </c>
-      <c r="H91" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I91" s="11" t="s">
+      <c r="I91" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J91" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J91" s="11" t="s">
+      <c r="K91" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="K91" s="11" t="s">
+      <c r="L91" s="11" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A92" s="11" t="s">
         <v>629</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="11"/>
+      <c r="C92" s="11" t="s">
         <v>529</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="D92" s="11" t="s">
         <v>530</v>
       </c>
-      <c r="D92" s="13">
+      <c r="E92" s="13">
         <v>31819.428</v>
       </c>
-      <c r="E92" s="13">
+      <c r="F92" s="13">
         <v>28318.5</v>
       </c>
-      <c r="F92" s="56">
+      <c r="G92" s="56">
         <f t="shared" si="2"/>
         <v>-3500.9279999999999</v>
       </c>
-      <c r="G92" s="12">
+      <c r="H92" s="12">
         <v>46204</v>
       </c>
-      <c r="H92" s="12">
-        <v>46234</v>
-      </c>
-      <c r="I92" s="11" t="s">
+      <c r="I92" s="12">
+        <v>46234</v>
+      </c>
+      <c r="J92" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="J92" s="11" t="s">
+      <c r="K92" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="K92" s="11" t="s">
+      <c r="L92" s="11" t="s">
         <v>340</v>
       </c>
     </row>
